--- a/resultados/2026-10-19/prospeccao.xlsx
+++ b/resultados/2026-10-19/prospeccao.xlsx
@@ -566,77 +566,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>agro_digital_ia</t>
+          <t>carbono_restauracao</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Agricultura digital, IA e agricultura de precisão</t>
+          <t>Mercado de carbono, restauração e pagamento por serviços ambientais</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11342</v>
+        <v>10384</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9766710167983106</v>
+        <v>0.45807948025015</v>
       </c>
       <c r="E2" t="n">
-        <v>1173</v>
+        <v>265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7782548230449555</v>
+        <v>0.451218572242235</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>177</v>
+        <v>272</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1346153846153846</v>
+        <v>0.8133333333333332</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2316118935837246</v>
+        <v>-0.2935943060498221</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>77.3</v>
+        <v>75.7</v>
       </c>
       <c r="N2" t="n">
+        <v>37</v>
+      </c>
+      <c r="O2" t="n">
         <v>47</v>
       </c>
-      <c r="O2" t="n">
-        <v>84</v>
-      </c>
       <c r="P2" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="R2" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="S2" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="T2" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="U2" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="V2" t="n">
         <v>100</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Chamada de P&amp;D&amp;I em IA aplicada ao agro (modelos preditivos de safra, visão computacional, gêmeos digitais de fazenda) com contrapartida de cooperativas e startups.</t>
+          <t>Chamada de restauração produtiva (SAFs, adequação ao Código Florestal) com monitoramento por satélite e projetos jurisdicionais de carbono.</t>
         </is>
       </c>
     </row>
@@ -670,10 +670,10 @@
         <v>1045</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5978593272171253</v>
+        <v>0.3329081632653061</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
         <v>0.06382978723404253</v>
@@ -682,7 +682,7 @@
         <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>76.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>95</v>
@@ -694,7 +694,7 @@
         <v>89</v>
       </c>
       <c r="Q3" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="R3" t="n">
         <v>68</v>
@@ -706,7 +706,7 @@
         <v>89</v>
       </c>
       <c r="U3" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="V3" t="n">
         <v>50</v>
@@ -720,77 +720,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>carbono_restauracao</t>
+          <t>agro_digital_ia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mercado de carbono, restauração e pagamento por serviços ambientais</t>
+          <t>Agricultura digital, IA e agricultura de precisão</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10384</v>
+        <v>11342</v>
       </c>
       <c r="D4" t="n">
-        <v>0.45807948025015</v>
+        <v>0.9766710167983106</v>
       </c>
       <c r="E4" t="n">
-        <v>265</v>
+        <v>1173</v>
       </c>
       <c r="F4" t="n">
-        <v>0.451218572242235</v>
+        <v>0.7782548230449555</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>272</v>
+        <v>177</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8133333333333332</v>
+        <v>0.1346153846153846</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2935943060498221</v>
+        <v>-0.2316118935837246</v>
       </c>
       <c r="L4" t="n">
         <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>74.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="P4" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="R4" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="S4" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="T4" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="V4" t="n">
         <v>100</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Chamada de restauração produtiva (SAFs, adequação ao Código Florestal) com monitoramento por satélite e projetos jurisdicionais de carbono.</t>
+          <t>Chamada de P&amp;D&amp;I em IA aplicada ao agro (modelos preditivos de safra, visão computacional, gêmeos digitais de fazenda) com contrapartida de cooperativas e startups.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>0.07843137254901955</v>
       </c>
       <c r="J5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
         <v>-0.2138810198300283</v>
@@ -836,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
       <c r="N5" t="n">
         <v>32</v>
@@ -848,7 +848,7 @@
         <v>84</v>
       </c>
       <c r="Q5" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="R5" t="n">
         <v>84</v>
@@ -904,7 +904,7 @@
         <v>-0.1611111111111111</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
         <v>-0.4186795491143317</v>
@@ -913,7 +913,7 @@
         <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>71.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="N6" t="n">
         <v>89</v>
@@ -925,7 +925,7 @@
         <v>66</v>
       </c>
       <c r="Q6" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="R6" t="n">
         <v>58</v>
@@ -990,7 +990,7 @@
         <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>61.1</v>
+        <v>62.2</v>
       </c>
       <c r="N7" t="n">
         <v>84</v>
@@ -1002,7 +1002,7 @@
         <v>97</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="R7" t="n">
         <v>5</v>
@@ -1067,7 +1067,7 @@
         <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>60.2</v>
+        <v>61.5</v>
       </c>
       <c r="N8" t="n">
         <v>79</v>
@@ -1079,7 +1079,7 @@
         <v>76</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="R8" t="n">
         <v>47</v>
@@ -1091,7 +1091,7 @@
         <v>94</v>
       </c>
       <c r="U8" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="V8" t="n">
         <v>75</v>
@@ -1135,7 +1135,7 @@
         <v>1.155172413793104</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>-0.2091254752851711</v>
@@ -1144,7 +1144,7 @@
         <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>60.2</v>
+        <v>58.9</v>
       </c>
       <c r="N9" t="n">
         <v>63</v>
@@ -1156,7 +1156,7 @@
         <v>58</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
         <v>79</v>
@@ -1182,154 +1182,154 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>agua_irrigacao</t>
+          <t>genetica_melhoramento</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Melhoramento genético, edição gênica e fenotipagem</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6172</v>
+        <v>11998</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3871068363926349</v>
+        <v>0.2061929073629738</v>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3027444026751491</v>
+        <v>-0.1811841474654378</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07971014492753614</v>
+        <v>0.4770642201834863</v>
       </c>
       <c r="J10" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01956947162426603</v>
+        <v>-0.3123425692695214</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
         <v>58.5</v>
       </c>
       <c r="N10" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="O10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>71</v>
+      </c>
+      <c r="R10" t="n">
         <v>42</v>
       </c>
-      <c r="P10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>16</v>
+      </c>
+      <c r="T10" t="n">
+        <v>33</v>
+      </c>
+      <c r="U10" t="n">
+        <v>66</v>
+      </c>
+      <c r="V10" t="n">
         <v>100</v>
       </c>
-      <c r="R10" t="n">
-        <v>63</v>
-      </c>
-      <c r="S10" t="n">
-        <v>58</v>
-      </c>
-      <c r="T10" t="n">
-        <v>83</v>
-      </c>
-      <c r="U10" t="n">
-        <v>37</v>
-      </c>
-      <c r="V10" t="n">
-        <v>75</v>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Edital de irrigação eficiente em sequeiro/safrinha, gestão de bacias (Cabeceiras do Pantanal) e reúso de efluentes agroindustriais.</t>
+          <t>Edital de melhoramento e fenotipagem de alto rendimento para soja, milho, algodão e forrageiras adaptadas ao Cerrado/transição Amazônia.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>genetica_melhoramento</t>
+          <t>agua_irrigacao</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Melhoramento genético, edição gênica e fenotipagem</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11998</v>
+        <v>6172</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2061929073629738</v>
+        <v>0.3871068363926349</v>
       </c>
       <c r="E11" t="n">
+        <v>143</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3027444026751491</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>149</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.07971014492753614</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.01956947162426603</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>21</v>
+      </c>
+      <c r="O11" t="n">
         <v>42</v>
       </c>
-      <c r="F11" t="n">
-        <v>-0.1811841474654378</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>161</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.4770642201834863</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.3123425692695214</v>
-      </c>
-      <c r="L11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="N11" t="n">
-        <v>53</v>
-      </c>
-      <c r="O11" t="n">
-        <v>16</v>
-      </c>
       <c r="P11" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="R11" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="T11" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="U11" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="V11" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Edital de melhoramento e fenotipagem de alto rendimento para soja, milho, algodão e forrageiras adaptadas ao Cerrado/transição Amazônia.</t>
+          <t>Edital de irrigação eficiente em sequeiro/safrinha, gestão de bacias (Cabeceiras do Pantanal) e reúso de efluentes agroindustriais.</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>57.5</v>
+        <v>58.1</v>
       </c>
       <c r="N12" t="n">
         <v>11</v>
@@ -1387,7 +1387,7 @@
         <v>50</v>
       </c>
       <c r="Q12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="R12" t="n">
         <v>89</v>
@@ -1443,7 +1443,7 @@
         <v>0.2222222222222223</v>
       </c>
       <c r="J13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
         <v>-0.9447236180904522</v>
@@ -1520,7 +1520,7 @@
         <v>0.06743566992014194</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
         <v>-0.1332436069986541</v>
@@ -1567,304 +1567,304 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bioenergia_combustiveis</t>
+          <t>rastreabilidade_desmatamento</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bioenergia, etanol de milho e combustíveis sustentáveis</t>
+          <t>Rastreabilidade e cadeias livres de desmatamento (EUDR)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7761</v>
+        <v>1099</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.05281813798853774</v>
+        <v>3.519531737076294</v>
       </c>
       <c r="E15" t="n">
-        <v>436</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>2.125032490415521</v>
+        <v>1.761878867676103</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>541</v>
+        <v>84</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5818713450292399</v>
+        <v>-0.3170731707317073</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>-0.1657032755298651</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>52.1</v>
+        <v>53.1</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="P15" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="R15" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
-      </c>
-      <c r="T15" t="n">
-        <v>67</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="V15" t="n">
         <v>100</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Edital de coprodutos do etanol de milho (DDGS, óleo, biometano de vinhaça) e rotas para SAF/diesel verde a partir de culturas e resíduos regionais.</t>
+          <t>Edital de plataformas de rastreabilidade de soja, carne e algodão (CAR, GTA, monitoramento) para adequação às exigências do mercado europeu.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rastreabilidade_desmatamento</t>
+          <t>bioenergia_combustiveis</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rastreabilidade e cadeias livres de desmatamento (EUDR)</t>
+          <t>Bioenergia, etanol de milho e combustíveis sustentáveis</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1099</v>
+        <v>7761</v>
       </c>
       <c r="D16" t="n">
-        <v>3.519531737076294</v>
+        <v>-0.05281813798853774</v>
       </c>
       <c r="E16" t="n">
-        <v>34</v>
+        <v>436</v>
       </c>
       <c r="F16" t="n">
-        <v>1.761878867676103</v>
+        <v>2.125032490415521</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>84</v>
+        <v>541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3170731707317073</v>
+        <v>0.5818713450292399</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.1657032755298651</v>
+      </c>
       <c r="L16" t="n">
         <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>52</v>
+        <v>52.4</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="O16" t="n">
+        <v>68</v>
+      </c>
+      <c r="P16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>26</v>
+      </c>
+      <c r="R16" t="n">
         <v>11</v>
       </c>
-      <c r="P16" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>34</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>100</v>
       </c>
-      <c r="S16" t="n">
-        <v>95</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>67</v>
+      </c>
       <c r="U16" t="n">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="V16" t="n">
         <v>100</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Edital de plataformas de rastreabilidade de soja, carne e algodão (CAR, GTA, monitoramento) para adequação às exigências do mercado europeu.</t>
+          <t>Edital de coprodutos do etanol de milho (DDGS, óleo, biometano de vinhaça) e rotas para SAF/diesel verde a partir de culturas e resíduos regionais.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>economia_circular</t>
+          <t>manejo_fogo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Economia circular, biomateriais e resíduos do agro</t>
+          <t>Manejo integrado do fogo e queimadas</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26563</v>
+        <v>10642</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09014932988217961</v>
+        <v>0.04904255804476554</v>
       </c>
       <c r="E17" t="n">
-        <v>315</v>
+        <v>514</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1125550731200554</v>
+        <v>0.02252514140613449</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>119</v>
+        <v>1281</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1226415094339623</v>
+        <v>0.1148825065274151</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6343381389252949</v>
+        <v>0.4282051282051282</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="N17" t="n">
+        <v>42</v>
+      </c>
+      <c r="O17" t="n">
         <v>74</v>
       </c>
-      <c r="O17" t="n">
-        <v>58</v>
-      </c>
       <c r="P17" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="Q17" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="R17" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="S17" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="T17" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="U17" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="V17" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Chamada de valorização de resíduos (palha, caroço de algodão, torta, bagaço) em biomateriais, bioinsumos e energia.</t>
+          <t>Chamada de prevenção e alerta precoce de incêndios (Pantanal, Cerrado, Amazônia) com tecnologia, manejo do fogo e brigadas comunitárias.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>manejo_fogo</t>
+          <t>economia_circular</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Manejo integrado do fogo e queimadas</t>
+          <t>Economia circular, biomateriais e resíduos do agro</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10642</v>
+        <v>26563</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04904255804476554</v>
+        <v>0.09014932988217961</v>
       </c>
       <c r="E18" t="n">
-        <v>514</v>
+        <v>315</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02252514140613449</v>
+        <v>-0.1125550731200554</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>1281</v>
+        <v>119</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1148825065274151</v>
+        <v>0.1226415094339623</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4282051282051282</v>
+        <v>-0.6343381389252949</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="N18" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="O18" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="P18" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>63</v>
+      </c>
+      <c r="R18" t="n">
+        <v>26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>26</v>
+      </c>
+      <c r="T18" t="n">
         <v>11</v>
       </c>
-      <c r="Q18" t="n">
-        <v>13</v>
-      </c>
-      <c r="R18" t="n">
-        <v>16</v>
-      </c>
-      <c r="S18" t="n">
-        <v>47</v>
-      </c>
-      <c r="T18" t="n">
-        <v>100</v>
-      </c>
       <c r="U18" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Chamada de prevenção e alerta precoce de incêndios (Pantanal, Cerrado, Amazônia) com tecnologia, manejo do fogo e brigadas comunitárias.</t>
+          <t>Chamada de valorização de resíduos (palha, caroço de algodão, torta, bagaço) em biomateriais, bioinsumos e energia.</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
         <v>0.1111111111111112</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>-0.2339688041594454</v>
@@ -1910,7 +1910,7 @@
         <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>45.9</v>
+        <v>44</v>
       </c>
       <c r="N19" t="n">
         <v>68</v>
@@ -1922,7 +1922,7 @@
         <v>29</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="R19" t="n">
         <v>21</v>
@@ -1978,7 +1978,7 @@
         <v>0.2820512820512822</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>-0.3826086956521739</v>
@@ -1987,7 +1987,7 @@
         <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>39.2</v>
+        <v>38.6</v>
       </c>
       <c r="N20" t="n">
         <v>58</v>
@@ -1999,7 +1999,7 @@
         <v>11</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
         <v>32</v>
@@ -5143,10 +5143,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="57" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -5203,154 +5203,154 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://fapesp.br/oportunidades</t>
+          <t>https://fapesp.br/oportunidades/centro-de-inovacao-em-resiliencia-urbana-e-energetica-(cirue)/9875/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agricultura digital, IA e agricultura de precisão</t>
+          <t>Agricultura regenerativa, carbono no solo e ILPF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Inteligência Artificial, Sistemas Digitais e Veiculares</t>
+          <t xml:space="preserve">A 37-year soil experiment revealed a hidden climate threat. The world's longest-running soil warming experiment has revealed an unexpected climate concern. After nearly four decades, researchers found that warming can cause microbes to break down stable soil carbon that scientists once believed was largely protected. That releases extra carbon dioxide into the atmosphere, potentially accelerating </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.sciencedaily.com/releases/2026/07/260713000809.htm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agricultura digital, IA e agricultura de precisão</t>
+          <t>Bioenergia, etanol de milho e combustíveis sustentáveis</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>Agência Fapesp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Inteligência Embarcada, Inteligência Artificial e Ciência de Dados</t>
+          <t>Enzima encontrada na raiz da cana aumenta em seis vezes a produção de açúcar a partir do bagaço. A reportagem mais acessada entre 9 e 15 de outubro detalha pesquisa de cientistas da USP que isolou a molécula ao estudar os aerênquimas – estruturas que a própria planta cria para formar canais de ar em suas raízes. O achado pode impulsionar a produção de etanol de segunda geração.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://agencia.fapesp.br/enzima-encontrada-na-raiz-da-cana-aumenta-em-seis-vezes-a-producao-de-acucar-a-partir-do-bagaco/59348</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agricultura digital, IA e agricultura de precisão</t>
+          <t>Mudanças climáticas, eventos extremos e adaptação</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>FAO Newsroom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>congresso</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sistemas de Visão Computacional, Inteligência Artificial e Conectividade</t>
+          <t>When El Niño brings drought, every minute counts</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.fao.org/newsroom/story/when-el-nino-brings-drought-every-minute-counts/en</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agricultura digital, IA e agricultura de precisão</t>
+          <t>Mudanças climáticas, eventos extremos e adaptação</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>Nature Sustainability</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sistemas Embarcados e Inteligência Artificial</t>
+          <t>Quantifying assets for the geopolitics of climate change mitigation.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.nature.com/articles/s41893-026-01971-z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bioinsumos e controle biológico</t>
+          <t>Mudanças climáticas, eventos extremos e adaptação</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>Nature Climate Change</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bioinsumos e Processos Biotecnológicos Aplicados à Agricultura</t>
+          <t>Rare diseases are an overlooked dimension in climate–health adaptation.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.nature.com/articles/s41558-026-02770-2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agricultura regenerativa, carbono no solo e ILPF</t>
+          <t>Mudanças climáticas, eventos extremos e adaptação</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>Nature Climate Change</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5360,66 +5360,66 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A 37-year soil experiment revealed a hidden climate threat. The world's longest-running soil warming experiment has revealed an unexpected climate concern. After nearly four decades, researchers found that warming can cause microbes to break down stable soil carbon that scientists once believed was largely protected. That releases extra carbon dioxide into the atmosphere, potentially accelerating </t>
+          <t>Climate choices and attention are shaped more by politics than weather.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/07/260713000809.htm</t>
+          <t>https://www.nature.com/articles/s41558-026-02775-x</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bioenergia, etanol de milho e combustíveis sustentáveis</t>
+          <t>Mudanças climáticas, eventos extremos e adaptação</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>Nature Climate Change</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Processamento de Biomassa para Biocombustíveis</t>
+          <t>Political affiliation impacts climate attention and choice beyond extreme weather exposure.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.nature.com/articles/s41558-026-02765-z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bioenergia, etanol de milho e combustíveis sustentáveis</t>
+          <t>Mudanças climáticas, eventos extremos e adaptação</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agência Fapesp</t>
+          <t>Nature Climate Change</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Enzima encontrada na raiz da cana aumenta em seis vezes a produção de açúcar a partir do bagaço. A reportagem mais acessada entre 9 e 15 de outubro detalha pesquisa de cientistas da USP que isolou a molécula ao estudar os aerênquimas – estruturas que a própria planta cria para formar canais de ar em suas raízes. O achado pode impulsionar a produção de etanol de segunda geração.</t>
+          <t>Combining climate policy instruments for a just transition to a climate-neutral economy.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://agencia.fapesp.br/enzima-encontrada-na-raiz-da-cana-aumenta-em-seis-vezes-a-producao-de-acucar-a-partir-do-bagaco/59348</t>
+          <t>https://www.nature.com/articles/s41558-026-02757-z</t>
         </is>
       </c>
     </row>
@@ -5431,22 +5431,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FAO Newsroom</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>congresso</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>When El Niño brings drought, every minute counts</t>
+          <t xml:space="preserve">A 24-year study uncovers a surprising climate benefit beneath forests. Scientists have discovered that some forest soils are becoming surprisingly better at removing methane from the atmosphere as temperatures rise and rainfall declines. A study spanning up to 24 years found methane absorption increasing by an average of 3% annually, challenging previous predictions about climate change's effects </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.fao.org/newsroom/story/when-el-nino-brings-drought-every-minute-counts/en</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261014015525.htm</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nature Sustainability</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Quantifying assets for the geopolitics of climate change mitigation.</t>
+          <t>These tropical trees breathe at night to survive drought. Some tropical trees have evolved a clever way to survive drought by taking in carbon dioxide at night, allowing them to keep their pores closed during the hot daytime and conserve water. By comparing three Clusia species, researchers discovered that this water-saving form of photosynthesis, known as CAM, did not arise through a single evolu</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41893-026-01971-z</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260922005712.htm</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nature Climate Change</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rare diseases are an overlooked dimension in climate–health adaptation.</t>
+          <t>Plants may be evolving the wrong traits for a warming world. Morning glories may be getting caught in an evolutionary tug-of-war between surviving climate change and attracting increasingly scarce pollinators. Over just nine years, researchers found that the plants’ rate of adaptation plunged by 96%, even though they still had plenty of genetic diversity to evolve.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41558-026-02770-2</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260901010719.htm</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nature Climate Change</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Climate choices and attention are shaped more by politics than weather.</t>
+          <t>Ancient Arctic carbon is pouring into the sea, but the seabed captures most of it. Thawing Arctic permafrost is releasing ancient carbon into the ocean, raising fears that microbes could turn it into greenhouse gases and accelerate climate change. But sediment cores collected near Canada’s Herschel Island reveal a more reassuring twist: most of this land-based carbon becomes buried in the seafloor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41558-026-02775-x</t>
+          <t>https://www.sciencedaily.com/releases/2026/08/260802223424.htm</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nature Climate Change</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Political affiliation impacts climate attention and choice beyond extreme weather exposure.</t>
+          <t xml:space="preserve">A 37-year soil experiment revealed a hidden climate threat. The world's longest-running soil warming experiment has revealed an unexpected climate concern. After nearly four decades, researchers found that warming can cause microbes to break down stable soil carbon that scientists once believed was largely protected. That releases extra carbon dioxide into the atmosphere, potentially accelerating </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41558-026-02765-z</t>
+          <t>https://www.sciencedaily.com/releases/2026/07/260713000809.htm</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nature Climate Change</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Combining climate policy instruments for a just transition to a climate-neutral economy.</t>
+          <t>These bees have nowhere to hide from extreme heat. A major study of Australian native bees found that stem-nesting species may be the first to feel the impact of climate change. Unlike bees that nest underground, they have few ways to escape dangerous heat. Researchers also discovered that tropical bees are particularly vulnerable, even when they are already adapted to hot environments. The findin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41558-026-02757-z</t>
+          <t>https://www.sciencedaily.com/releases/2026/06/260617032157.htm</t>
         </is>
       </c>
     </row>
@@ -5603,12 +5603,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">A 24-year study uncovers a surprising climate benefit beneath forests. Scientists have discovered that some forest soils are becoming surprisingly better at removing methane from the atmosphere as temperatures rise and rainfall declines. A study spanning up to 24 years found methane absorption increasing by an average of 3% annually, challenging previous predictions about climate change's effects </t>
+          <t>A hidden pollutant is changing how the world's forests breathe. A massive global analysis found that nitrogen pollution can either speed up or dramatically slow the natural "breathing" of forest soils, depending on the ecosystem's condition. The results reveal hidden tipping points that could affect how forests store carbon and cope with climate change.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261014015525.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/06/260602021659.htm</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>These tropical trees breathe at night to survive drought. Some tropical trees have evolved a clever way to survive drought by taking in carbon dioxide at night, allowing them to keep their pores closed during the hot daytime and conserve water. By comparing three Clusia species, researchers discovered that this water-saving form of photosynthesis, known as CAM, did not arise through a single evolu</t>
+          <t>NASA discovers hidden fires burning beneath the Amazon rainforest. El Niño is fueling a dangerous cascade of wildfires across the tropics, with the Amazon rainforest now experiencing widespread burning and scientists warning that the worst may still be ahead. NASA researchers are uncovering dozens of previously undetected fires, suggesting the destruction could be even more extensive than satellit</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260922005712.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261016070633.htm</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Plants may be evolving the wrong traits for a warming world. Morning glories may be getting caught in an evolutionary tug-of-war between surviving climate change and attracting increasingly scarce pollinators. Over just nine years, researchers found that the plants’ rate of adaptation plunged by 96%, even though they still had plenty of genetic diversity to evolve.</t>
+          <t xml:space="preserve">A 24-year study uncovers a surprising climate benefit beneath forests. Scientists have discovered that some forest soils are becoming surprisingly better at removing methane from the atmosphere as temperatures rise and rainfall declines. A study spanning up to 24 years found methane absorption increasing by an average of 3% annually, challenging previous predictions about climate change's effects </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260901010719.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261014015525.htm</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5684,12 +5684,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ancient Arctic carbon is pouring into the sea, but the seabed captures most of it. Thawing Arctic permafrost is releasing ancient carbon into the ocean, raising fears that microbes could turn it into greenhouse gases and accelerate climate change. But sediment cores collected near Canada’s Herschel Island reveal a more reassuring twist: most of this land-based carbon becomes buried in the seafloor</t>
+          <t>These tropical trees breathe at night to survive drought. Some tropical trees have evolved a clever way to survive drought by taking in carbon dioxide at night, allowing them to keep their pores closed during the hot daytime and conserve water. By comparing three Clusia species, researchers discovered that this water-saving form of photosynthesis, known as CAM, did not arise through a single evolu</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/08/260802223424.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260922005712.htm</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">A 37-year soil experiment revealed a hidden climate threat. The world's longest-running soil warming experiment has revealed an unexpected climate concern. After nearly four decades, researchers found that warming can cause microbes to break down stable soil carbon that scientists once believed was largely protected. That releases extra carbon dioxide into the atmosphere, potentially accelerating </t>
+          <t xml:space="preserve">Irrigation’s climate benefit could equal 363 years of its own emissions. U.S. irrigation produces some greenhouse gas emissions, but new research suggests it prevents vastly more by allowing farmers to grow more food on less land. Without irrigation, replacing lost crop yields could require converting natural ecosystems into farmland, releasing an estimated 6.86 gigatons of greenhouse gases. That </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/07/260713000809.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260915232119.htm</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>These bees have nowhere to hide from extreme heat. A major study of Australian native bees found that stem-nesting species may be the first to feel the impact of climate change. Unlike bees that nest underground, they have few ways to escape dangerous heat. Researchers also discovered that tropical bees are particularly vulnerable, even when they are already adapted to hot environments. The findin</t>
+          <t>Global warming is breaking a 400-year climate link between two oceans. The Indian and Pacific oceans have been climatically linked for centuries, but scientists say that connection is now breaking down in an exceptional way. Ancient climate records suggest volcanoes disrupted the relationship in the past, while today human-caused warming appears to be driving a much more unusual shift.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/06/260617032157.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260912220029.htm</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A hidden pollutant is changing how the world's forests breathe. A massive global analysis found that nitrogen pollution can either speed up or dramatically slow the natural "breathing" of forest soils, depending on the ecosystem's condition. The results reveal hidden tipping points that could affect how forests store carbon and cope with climate change.</t>
+          <t>Indonesia’s most dangerous fires are burning underground. Indonesia’s dangerous peat fires are surging early in the 2026 fire season as a strengthening El Niño and severe drought dry out wetlands that can burn underground for months. These slow smoldering fires are especially destructive because they release far more fine particles and several pollutants than typical tropical forest fires, while t</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/06/260602021659.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260904000318.htm</t>
         </is>
       </c>
     </row>
@@ -5792,12 +5792,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NASA discovers hidden fires burning beneath the Amazon rainforest. El Niño is fueling a dangerous cascade of wildfires across the tropics, with the Amazon rainforest now experiencing widespread burning and scientists warning that the worst may still be ahead. NASA researchers are uncovering dozens of previously undetected fires, suggesting the destruction could be even more extensive than satellit</t>
+          <t xml:space="preserve">Extreme drought now covers 44% of Puerto Rico. Puerto Rico’s normally rainy season has instead brought a severe and fast-growing drought. By August 25, three-quarters of the territory was in at least moderate drought, with extreme drought covering 44 percent and some areas receiving less than 20 percent of their usual rainfall. Water shortages have forced rationing, while farmers are losing crops </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261016070633.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260902234457.htm</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">A 24-year study uncovers a surprising climate benefit beneath forests. Scientists have discovered that some forest soils are becoming surprisingly better at removing methane from the atmosphere as temperatures rise and rainfall declines. A study spanning up to 24 years found methane absorption increasing by an average of 3% annually, challenging previous predictions about climate change's effects </t>
+          <t>Earth may have lost the Sun’s protective shield millions of years ago. NASA-funded studies suggest Earth’s climate has been influenced by both the Sun’s travels through dense regions of the Milky Way and the violent superflares of its youth. Those events may help explain ancient ice ages as well as how early Earth stayed warm enough for liquid water when the Sun was much dimmer.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261014015525.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260901070523.htm</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>These tropical trees breathe at night to survive drought. Some tropical trees have evolved a clever way to survive drought by taking in carbon dioxide at night, allowing them to keep their pores closed during the hot daytime and conserve water. By comparing three Clusia species, researchers discovered that this water-saving form of photosynthesis, known as CAM, did not arise through a single evolu</t>
+          <t>Plants may be evolving the wrong traits for a warming world. Morning glories may be getting caught in an evolutionary tug-of-war between surviving climate change and attracting increasingly scarce pollinators. Over just nine years, researchers found that the plants’ rate of adaptation plunged by 96%, even though they still had plenty of genetic diversity to evolve.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260922005712.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260901010719.htm</t>
         </is>
       </c>
     </row>
@@ -5873,12 +5873,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Irrigation’s climate benefit could equal 363 years of its own emissions. U.S. irrigation produces some greenhouse gas emissions, but new research suggests it prevents vastly more by allowing farmers to grow more food on less land. Without irrigation, replacing lost crop yields could require converting natural ecosystems into farmland, releasing an estimated 6.86 gigatons of greenhouse gases. That </t>
+          <t>One of Earth’s driest places was just covered in snow. Rare storms covered huge stretches of Chile’s Atacama Desert in snow and dumped extraordinary amounts of rain on one of the driest regions on Earth. The extreme weather shut down observatories, triggered damaging floods and mudflows, and unfolded against the backdrop of a strengthening El Niño.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260915232119.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260901010709.htm</t>
         </is>
       </c>
     </row>
@@ -5890,22 +5890,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Global warming is breaking a 400-year climate link between two oceans. The Indian and Pacific oceans have been climatically linked for centuries, but scientists say that connection is now breaking down in an exceptional way. Ancient climate records suggest volcanoes disrupted the relationship in the past, while today human-caused warming appears to be driving a much more unusual shift.</t>
+          <t>Conservation is bringing species back. Governments must help those gains last. &amp;#160; An old elephant can remember where to find water when the usual pools have dried. Her death leaves the herd with fewer ways to survive a drought. As elephants travel, they also carry seeds in their guts, depositing them far from the trees where they fed. In a forest emptied of large birds and [&amp;#8230;]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260912220029.htm</t>
+          <t>https://news.mongabay.com/2026/10/conservation-is-bringing-species-back-governments-must-help-those-gains-last/</t>
         </is>
       </c>
     </row>
@@ -5917,184 +5917,184 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Indonesia’s most dangerous fires are burning underground. Indonesia’s dangerous peat fires are surging early in the 2026 fire season as a strengthening El Niño and severe drought dry out wetlands that can burn underground for months. These slow smoldering fires are especially destructive because they release far more fine particles and several pollutants than typical tropical forest fires, while t</t>
+          <t>Climate change could send more toxic mining waste into coastal waters, study warns. Demand for metals has exploded in recent decades, thanks to population growth, technological innovation, and economic development. The volume of metal ores like iron and copper extracted globally quadrupled during the last half-century, and the trillion-dollar industry shows no signs of slowing down. But the growin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260904000318.htm</t>
+          <t>https://news.mongabay.com/2026/10/climate-change-could-send-more-toxic-mining-waste-into-coastal-waters-study-warns/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mudanças climáticas, eventos extremos e adaptação</t>
+          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Fundo Amazônia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extreme drought now covers 44% of Puerto Rico. Puerto Rico’s normally rainy season has instead brought a severe and fast-growing drought. By August 25, three-quarters of the territory was in at least moderate drought, with extreme drought covering 44 percent and some areas receiving less than 20 percent of their usual rainfall. Water shortages have forced rationing, while farmers are losing crops </t>
+          <t>Fundo Amazônia em Números</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260902234457.htm</t>
+          <t>https://www.fundoamazonia.gov.br/pt/monitoramento-e-avaliacao/fundo-amazonia-em-numeros/index.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mudanças climáticas, eventos extremos e adaptação</t>
+          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Fundo Amazônia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Earth may have lost the Sun’s protective shield millions of years ago. NASA-funded studies suggest Earth’s climate has been influenced by both the Sun’s travels through dense regions of the Milky Way and the violent superflares of its youth. Those events may help explain ancient ice ages as well as how early Earth stayed warm enough for liquid water when the Sun was much dimmer.</t>
+          <t>Fundação Banco do Brasil - Fundo Amazônia Fundação Banco do Brasil (FBB)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260901070523.htm</t>
+          <t>https://www.fundoamazonia.gov.br/pt/projeto/Fundacao-Banco-do-Brasil-Fundo-Amazonia/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mudanças climáticas, eventos extremos e adaptação</t>
+          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Fundo Amazônia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Plants may be evolving the wrong traits for a warming world. Morning glories may be getting caught in an evolutionary tug-of-war between surviving climate change and attracting increasingly scarce pollinators. Over just nine years, researchers found that the plants’ rate of adaptation plunged by 96%, even though they still had plenty of genetic diversity to evolve.</t>
+          <t>Fortalecimento da Gestão Territorial e Ambiental de Terras Indígenas na Amazônia The Nature Conservancy do Brasil (TNC Brasil)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260901010719.htm</t>
+          <t>https://www.fundoamazonia.gov.br/pt/projeto/Fortalecimento-da-Gestao-Territorial-e-Ambiental-de-Terras-Indigenas-na-Amazonia/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mudanças climáticas, eventos extremos e adaptação</t>
+          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>CAPES - Editais</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>One of Earth’s driest places was just covered in snow. Rare storms covered huge stretches of Chile’s Atacama Desert in snow and dumped extraordinary amounts of rain on one of the driest regions on Earth. The extreme weather shut down observatories, triggered damaging floods and mudflows, and unfolded against the backdrop of a strengthening El Niño.</t>
+          <t>Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260901010709.htm</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/programas-estrategicos/desenvolvimento-regional/redes-de-pesquisa-e-desenvolvimento/programa-rede-de-pesquisa-e-desenvolvimento-da-amazonia-legal</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mudanças climáticas, eventos extremos e adaptação</t>
+          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>CAPES - Editais</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Conservation is bringing species back. Governments must help those gains last. &amp;#160; An old elephant can remember where to find water when the usual pools have dried. Her death leaves the herd with fewer ways to survive a drought. As elephants travel, they also carry seeds in their guts, depositing them far from the trees where they fed. In a forest emptied of large birds and [&amp;#8230;]</t>
+          <t>Programa de Desenvolvimento Acadêmico Indígena (PDAI)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/2026/10/conservation-is-bringing-species-back-governments-must-help-those-gains-last/</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/programas-estrategicos/desenvolvimento-regional/programa-de-desenvolvimento-academico-indigena-pdai</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mudanças climáticas, eventos extremos e adaptação</t>
+          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>Nature Climate Change</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Climate change could send more toxic mining waste into coastal waters, study warns. Demand for metals has exploded in recent decades, thanks to population growth, technological innovation, and economic development. The volume of metal ores like iron and copper extracted globally quadrupled during the last half-century, and the trillion-dollar industry shows no signs of slowing down. But the growin</t>
+          <t>Biodiversity and the Conferences of the Parties.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/2026/10/climate-change-could-send-more-toxic-mining-waste-into-coastal-waters-study-warns/</t>
+          <t>https://www.nature.com/articles/s41558-026-02792-w</t>
         </is>
       </c>
     </row>
@@ -6106,22 +6106,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>Nature Climate Change</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bioeconomia no agronegócio</t>
+          <t>Astrid Schomaker on biodiversity in a triple COP year.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.nature.com/articles/s41558-026-02778-8</t>
         </is>
       </c>
     </row>
@@ -6133,22 +6133,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Desenvolvimento Sustentável da Fruticultura na Amazônia</t>
+          <t>Scientists left this farm field alone. Thousands of orchids appeared. An abandoned farm field became a flourishing wildflower meadow within little more than a decade, with plant diversity doubling and thousands of orchids appearing naturally. The discovery suggests that simply giving nature time to recover could be a powerful and inexpensive tool for restoring biodiversity.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.sciencedaily.com/releases/2026/08/260822015208.htm</t>
         </is>
       </c>
     </row>
@@ -6160,22 +6160,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fundo Amazônia em Números</t>
+          <t>More trees can mean fewer birds, new study reveals. Trees planted to protect farmland from wind may not be the biodiversity boost many assume. In Japan’s wetland farming landscapes, shelterbelts benefited some birds but sharply reduced grassland and wetland species that need open space. Researchers found grassland bird abundance dropped by more than 70% near shelterbelts.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/home/</t>
+          <t>https://www.sciencedaily.com/releases/2026/06/260620100426.htm</t>
         </is>
       </c>
     </row>
@@ -6187,22 +6187,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Conheça mais números do Fundo Amazônia</t>
+          <t>NASA discovers hidden fires burning beneath the Amazon rainforest. El Niño is fueling a dangerous cascade of wildfires across the tropics, with the Amazon rainforest now experiencing widespread burning and scientists warning that the worst may still be ahead. NASA researchers are uncovering dozens of previously undetected fires, suggesting the destruction could be even more extensive than satellit</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/monitoramento-e-avaliacao/fundo-amazonia-em-numeros/index.html</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261016070633.htm</t>
         </is>
       </c>
     </row>
@@ -6214,22 +6214,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Produção sustentável Atividades que mantêm a floresta em pé têm atratividade econômica</t>
+          <t>A Belgium-sized area of Amazon wetland has been converted, and losses are climbing. Every year, Amazonian rivers spill over their banks and flood the forests around them for months. These wetlands cover around 30% of the Brazilian Amazon and are often home to riverine families, who live in adapted homes built on stilts. They fish and plant crops with the natural ebb and flow of the rivers. But [&amp;#</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/home/</t>
+          <t>https://news.mongabay.com/short-article/2026/10/a-belgium-sized-area-of-amazon-wetland-has-been-converted-and-losses-are-climbing/</t>
         </is>
       </c>
     </row>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Atividades que mantêm a floresta em pé têm atratividade econômica</t>
+          <t>Nearly 90% of countries adopt biodiversity targets, but most remain off track. Thousands of delegates are now gathering in Yerevan to discuss the future of life on Earth as we know it at the U.N.’s COP17 biodiversity summit. Countries have made considerable progress in developing national conservation plans under the biodiversity framework agreed to at COP15 in Montreal in 2022, but most remain we</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/home/</t>
+          <t>https://news.mongabay.com/2026/10/nearly-90-of-countries-adopt-biodiversity-targets-but-most-remain-off-track/</t>
         </is>
       </c>
     </row>
@@ -6268,22 +6268,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ordenamento territorial Área da Amazônia Legal está ordenada territorialmente</t>
+          <t>Amazon deforestation falls 42% to a record low. Deforestation in the Brazilian Amazon has fallen to the lowest level on record. Data released today by Brazil&amp;#8217;s national space research institute, INPE, shows that forest clearing in Earth&amp;#8217;s largest rainforest over the 12 months ended July 31, 2026, amounted to 3,335 square kilometers (1,288 square miles), an area smaller than the Spanish</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/home/</t>
+          <t>https://news.mongabay.com/short-article/2026/10/amazon-deforestation-falls-42-to-a-record-low/</t>
         </is>
       </c>
     </row>
@@ -6295,22 +6295,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Área da Amazônia Legal está ordenada territorialmente</t>
+          <t>Fundraising to protect oceans, forests and other key nature sites falling short ahead of UN summit. Promises by nations to spend hundreds of billions of dollars to finance nature and increase protections for oceans around the globe are falling short ahead of a key U.N. biodiversity conference. The warnings from the head of the conference and environmental groups comes as the countries gather Monda</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/home/</t>
+          <t>https://news.mongabay.com/short-article/2026/10/fundraising-to-protect-oceans-forests-and-other-key-nature-sites-falling-short-ahead-of-un-summit/</t>
         </is>
       </c>
     </row>
@@ -6322,34 +6322,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ciência, inovação e instrumentos econômicos Instrumentos econômicos e atividades de ciência, tecnologia e inovação contribuem para a recuperação, a conservação e o uso sustentável da biodiversidade</t>
+          <t>New tool reveals siege on Indigenous lands in Bolivia’s Amazon. For most Indigenous peoples in the Bolivian Amazon, the forest is far more than a collection of trees. It is the casa grande, Spanish for “the main house”, where communities, rivers, wildlife, spiritual beings and ancestral memories coexist. For them, conserving the forest means conserving life itself. Yet data analyzed by Amazonía Tr</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/home/</t>
+          <t>https://news.mongabay.com/2026/10/new-tool-reveals-siege-on-indigenous-lands-in-bolivias-amazon/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Mercado de carbono, restauração e pagamento por serviços ambientais</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>FAPESP - Oportunidades</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6359,208 +6359,208 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Instrumentos econômicos e atividades de ciência, tecnologia e inovação contribuem para a recuperação, a conservação e o uso sustentável da biodiversidade</t>
+          <t>Bolsa 1 – Digital Twin e restauração da rede O bolsista desenvolverá um modelo de Gêmeo Digital para simular a operação de estações de recarga de ônibus elétricos em situações de eventos climáticos extremos e propor estratégias de restauração da rede de distribuição por meio de...</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/home/</t>
+          <t>https://fapesp.br/oportunidades/centro-de-inovacao-em-resiliencia-urbana-e-energetica-(cirue)/9875/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Mercado de carbono, restauração e pagamento por serviços ambientais</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fundação Banco do Brasil - Fundo Amazônia Fundação Banco do Brasil (FBB)</t>
+          <t>Indonesian women cash in on mangrove restoration: Interview with community leader Wisye Sahambangung. JAKARTA — Wisye Sahambangung is a fisher, community leader, and mangrove conservationist from Sarawet, a coastal Indonesian village in North Sulawesi province. Since 2022, the 45-year-old has led Rhizopora, a women’s group that restores mangroves and helps create economic opportunities for women i</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/projeto/Fundacao-Banco-do-Brasil-Fundo-Amazonia/</t>
+          <t>https://news.mongabay.com/2026/10/indonesian-women-cash-in-on-mangrove-restoration-interview-with-community-leader-wisye-sahambangung/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Mercado de carbono, restauração e pagamento por serviços ambientais</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>Agência Fapesp</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fortalecimento da Gestão Territorial e Ambiental de Terras Indígenas na Amazônia The Nature Conservancy do Brasil (TNC Brasil)</t>
+          <t>Manejo adequado transforma pastagens degradadas em reservatórios de carbono. Experimentos de longa duração no interior paulista revelam que a intensificação moderada do pasto não apenas recupera a produtividade da terra, mas maximiza o sequestro de CO 2 . Pesquisa também validou método mais barato de medição</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/projeto/Fortalecimento-da-Gestao-Territorial-e-Ambiental-de-Terras-Indigenas-na-Amazonia/</t>
+          <t>https://agencia.fapesp.br/manejo-adequado-transforma-pastagens-degradadas-em-reservatorios-de-carbono/59417</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Rastreabilidade e cadeias livres de desmatamento (EUDR)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fundo Amazônia</t>
+          <t>Embrapa Notícias</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>WEBSÉRIE AFLUENTES: CAMINHOS E HISTÓRIAS DO FUNDO AMAZÔNIA</t>
+          <t>Encontro discutirá a rastreabilidade na cadeia de alimentos e produtos agropecuários</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.fundoamazonia.gov.br/pt/home/</t>
+          <t>https://www.embrapa.br/busca-de-noticias/-/noticia/148958203/encontro-discutira-a-rastreabilidade-na-cadeia-de-alimentos-e-produtos-agropecuarios?p_auth=sKBJQ0xo#p_buscanoticia_WAR_pcebusca</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Rastreabilidade e cadeias livres de desmatamento (EUDR)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAPES - Editais</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Programa Rede de Pesquisa e Desenvolvimento da Amazônia Legal</t>
+          <t>Amazon deforestation falls 42% to a record low. Deforestation in the Brazilian Amazon has fallen to the lowest level on record. Data released today by Brazil&amp;#8217;s national space research institute, INPE, shows that forest clearing in Earth&amp;#8217;s largest rainforest over the 12 months ended July 31, 2026, amounted to 3,335 square kilometers (1,288 square miles), an area smaller than the Spanish</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes</t>
+          <t>https://news.mongabay.com/short-article/2026/10/amazon-deforestation-falls-42-to-a-record-low/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAPES - Editais</t>
+          <t>Embrapa Notícias</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Programa de Desenvolvimento Acadêmico Indígena (PDAI)</t>
+          <t>Chefe-geral da Embrapa Gado de Corte integra lista das 100 Mulheres Poderosas do Agro</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes</t>
+          <t>https://www.embrapa.br/busca-de-noticias/-/noticia/148959410/chefe-geral-da-embrapa-gado-de-corte-integra-lista-das-100-mulheres-poderosas-do-agro?p_auth=sKBJQ0xo#p_buscanoticia_WAR_pcebusca</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nature Climate Change</t>
+          <t>CGIAR News</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Biodiversity and the Conferences of the Parties.</t>
+          <t>International Livestock Research Institute (ILRI)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41558-026-02792-w</t>
+          <t>https://www.ilri.org/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nature Climate Change</t>
+          <t>CGIAR News</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Astrid Schomaker on biodiversity in a triple COP year.</t>
+          <t>News October 16, 2026 How growing forage for livestock turned a small plot into a thriving family business In Ethiopia's Hadiya Zone, smallholder farmers are turning small plots of oats into profitable forage seed businesses that provide supplementary... internal</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41558-026-02778-8</t>
+          <t>https://www.cgiar.org/news-events/news/how-growing-forage-livestock-turned-small-plot-thriving-family-business</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6575,19 +6575,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Scientists left this farm field alone. Thousands of orchids appeared. An abandoned farm field became a flourishing wildflower meadow within little more than a decade, with plant diversity doubling and thousands of orchids appearing naturally. The discovery suggests that simply giving nature time to recover could be a powerful and inexpensive tool for restoring biodiversity.</t>
+          <t xml:space="preserve">A 24-year study uncovers a surprising climate benefit beneath forests. Scientists have discovered that some forest soils are becoming surprisingly better at removing methane from the atmosphere as temperatures rise and rainfall declines. A study spanning up to 24 years found methane absorption increasing by an average of 3% annually, challenging previous predictions about climate change's effects </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/08/260822015208.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261014015525.htm</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6602,24 +6602,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>More trees can mean fewer birds, new study reveals. Trees planted to protect farmland from wind may not be the biodiversity boost many assume. In Japan’s wetland farming landscapes, shelterbelts benefited some birds but sharply reduced grassland and wetland species that need open space. Researchers found grassland bird abundance dropped by more than 70% near shelterbelts.</t>
+          <t>The U.S. Eradicated this flesh-eating parasite. Now it’s back. The flesh eating New World screwworm has returned to the United States, threatening livestock, wildlife, pets and potentially people as it spreads north. A new UC San Diego tracking system aims to predict where the parasite could strike next while officials revive the eradication strategy that defeated it decades ago.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/06/260620100426.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260914102439.htm</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6629,105 +6629,105 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NASA discovers hidden fires burning beneath the Amazon rainforest. El Niño is fueling a dangerous cascade of wildfires across the tropics, with the Amazon rainforest now experiencing widespread burning and scientists warning that the worst may still be ahead. NASA researchers are uncovering dozens of previously undetected fires, suggesting the destruction could be even more extensive than satellit</t>
+          <t>Scientists finally solved how H5N1 bird flu hid in dairy cows. Researchers uncovered why H5N1 bird flu attacks cows’ udders instead of their lungs: the virus’s preferred receptors are concentrated in mammary tissue. The breakthrough could help scientists predict future bird flu jumps and spot unusual infections before they spread widely.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261016070633.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/06/260620100315.htm</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A Belgium-sized area of Amazon wetland has been converted, and losses are climbing. Every year, Amazonian rivers spill over their banks and flood the forests around them for months. These wetlands cover around 30% of the Brazilian Amazon and are often home to riverine families, who live in adapted homes built on stilts. They fish and plant crops with the natural ebb and flow of the rivers. But [&amp;#</t>
+          <t xml:space="preserve">A 24-year study uncovers a surprising climate benefit beneath forests. Scientists have discovered that some forest soils are becoming surprisingly better at removing methane from the atmosphere as temperatures rise and rainfall declines. A study spanning up to 24 years found methane absorption increasing by an average of 3% annually, challenging previous predictions about climate change's effects </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/short-article/2026/10/a-belgium-sized-area-of-amazon-wetland-has-been-converted-and-losses-are-climbing/</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261014015525.htm</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Nearly 90% of countries adopt biodiversity targets, but most remain off track. Thousands of delegates are now gathering in Yerevan to discuss the future of life on Earth as we know it at the U.N.’s COP17 biodiversity summit. Countries have made considerable progress in developing national conservation plans under the biodiversity framework agreed to at COP15 in Montreal in 2022, but most remain we</t>
+          <t>Scientists may have misread a 2-billion-year-old clue about Earth. Scientists have found that a famous 2-billion-year-old chemical signature, once thought to record a massive global change in Earth’s carbon cycle, may instead have been produced by local magma, hydrocarbons, and methane-eating microbes. The discovery raises new questions about what was really happening as oxygen transformed the you</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/2026/10/nearly-90-of-countries-adopt-biodiversity-targets-but-most-remain-off-track/</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260925093201.htm</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Amazon deforestation falls 42% to a record low. Deforestation in the Brazilian Amazon has fallen to the lowest level on record. Data released today by Brazil&amp;#8217;s national space research institute, INPE, shows that forest clearing in Earth&amp;#8217;s largest rainforest over the 12 months ended July 31, 2026, amounted to 3,335 square kilometers (1,288 square miles), an area smaller than the Spanish</t>
+          <t>Scientists stunned as volcano cloud starts destroying methane. The Hunga Tonga eruption may have triggered a surprising chemical reaction that destroyed some of the methane released into the atmosphere. Scientists say the discovery could reshape estimates of methane pollution and inspire new methods for slowing near-term global warming.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/short-article/2026/10/amazon-deforestation-falls-42-to-a-record-low/</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260915095750.htm</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Pecuária sustentável, metano e bem-estar animal</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>Agência Fapesp</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6737,78 +6737,78 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fundraising to protect oceans, forests and other key nature sites falling short ahead of UN summit. Promises by nations to spend hundreds of billions of dollars to finance nature and increase protections for oceans around the globe are falling short ahead of a key U.N. biodiversity conference. The warnings from the head of the conference and environmental groups comes as the countries gather Monda</t>
+          <t>Manejo adequado transforma pastagens degradadas em reservatórios de carbono. Experimentos de longa duração no interior paulista revelam que a intensificação moderada do pasto não apenas recupera a produtividade da terra, mas maximiza o sequestro de CO 2 . Pesquisa também validou método mais barato de medição</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/short-article/2026/10/fundraising-to-protect-oceans-forests-and-other-key-nature-sites-falling-short-ahead-of-un-summit/</t>
+          <t>https://agencia.fapesp.br/manejo-adequado-transforma-pastagens-degradadas-em-reservatorios-de-carbono/59417</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bioeconomia, sociobiodiversidade (Amazônia, Cerrado, Pantanal)</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>FAPESP - Oportunidades</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>New tool reveals siege on Indigenous lands in Bolivia’s Amazon. For most Indigenous peoples in the Bolivian Amazon, the forest is far more than a collection of trees. It is the casa grande, Spanish for “the main house”, where communities, rivers, wildlife, spiritual beings and ancestral memories coexist. For them, conserving the forest means conserving life itself. Yet data analyzed by Amazonía Tr</t>
+          <t>A pesquisa será desenvolvida no âmbito do CEPID CEMol e tem como foco a engenharia de superfície de fotoanodos semicondutores à base de BiVO4 e Fe2TiO5 para aplicação na divisão fotoeletroquímica da água visando à produção de hidrogênio verde. O projeto envolve a deposição de filmes...</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/2026/10/new-tool-reveals-siege-on-indigenous-lands-in-bolivias-amazon/</t>
+          <t>https://fapesp.br/oportunidades/engenharia-de-superficie-de-fotoanodos-de-bivo4-e-fe2tio5-para-divisao-fotoeletroquimica-da-Água/9914/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mercado de carbono, restauração e pagamento por serviços ambientais</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FAPESP - Oportunidades</t>
+          <t>FAO Newsroom</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>congresso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Bolsa 1 – Digital Twin e restauração da rede O bolsista desenvolverá um modelo de Gêmeo Digital para simular a operação de estações de recarga de ônibus elétricos em situações de eventos climáticos extremos e propor estratégias de restauração da rede de distribuição por meio de...</t>
+          <t>World Food Forum 2026: FAO calls for smarter water governance to safeguard food security</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://fapesp.br/oportunidades</t>
+          <t>https://www.fao.org/newsroom/detail/world-food-forum-2026--fao-calls-for-smarter-water-governance-to-safeguard-food-security/en</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mercado de carbono, restauração e pagamento por serviços ambientais</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>CGIAR News</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6818,24 +6818,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Indonesian women cash in on mangrove restoration: Interview with community leader Wisye Sahambangung. JAKARTA — Wisye Sahambangung is a fisher, community leader, and mangrove conservationist from Sarawet, a coastal Indonesian village in North Sulawesi province. Since 2022, the 45-year-old has led Rhizopora, a women’s group that restores mangroves and helps create economic opportunities for women i</t>
+          <t>CGIAR works with partners in six major regions to jointly address challenges to food, land, and water systems.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/2026/10/indonesian-women-cash-in-on-mangrove-restoration-interview-with-community-leader-wisye-sahambangung/</t>
+          <t>https://www.cgiar.org/cgiar-system</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mercado de carbono, restauração e pagamento por serviços ambientais</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agência Fapesp</t>
+          <t>CGIAR News</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6845,24 +6845,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Manejo adequado transforma pastagens degradadas em reservatórios de carbono. Experimentos de longa duração no interior paulista revelam que a intensificação moderada do pasto não apenas recupera a produtividade da terra, mas maximiza o sequestro de CO 2 . Pesquisa também validou método mais barato de medição</t>
+          <t>International Water Management Institute (IWMI)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://agencia.fapesp.br/manejo-adequado-transforma-pastagens-degradadas-em-reservatorios-de-carbono/59417</t>
+          <t>https://www.iwmi.org</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rastreabilidade e cadeias livres de desmatamento (EUDR)</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Embrapa Notícias</t>
+          <t>CGIAR News</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6872,213 +6872,213 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Encontro discutirá a rastreabilidade na cadeia de alimentos e produtos agropecuários</t>
+          <t>News October 16, 2026 Strengthening Local Leadership to Protect Fisheries and Water Resources in Cambodia In Cambodia’s Tonle Sap floodplains, water connects farms, fisheries, ecosystems and communities. internal</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.embrapa.br/busca-de-noticias/-/noticia/148958203/encontro-discutira-a-rastreabilidade-na-cadeia-de-alimentos-e-produtos-agropecuarios?p_auth=sKBJQ0xo#p_buscanoticia_WAR_pcebusca</t>
+          <t>https://www.cgiar.org/news-events/news/strengthening-local-leadership-protect-fisheries-and-water-resources-cambodia</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Rastreabilidade e cadeias livres de desmatamento (EUDR)</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Embrapa Notícias</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>O Agro em Código será realizado no dia 27 de outubro, em São Paulo (SP). Este é o maior encontro técnico sobre rastreabilidade do setor agropecuário brasileiro, envolvendo desde a origem da matéria...</t>
+          <t>New “plant armor” more than triples strawberry yields. A new protective fabric boosted strawberry yields by as much as 3.56 times while blocking insects and still allowing sunlight, rain, and airflow to reach the plants. Originally inspired by research on military clothing, Plant Armor could also help farms reduce pesticide and water use.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.embrapa.br/busca-de-noticias</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260930020257.htm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Rastreabilidade e cadeias livres de desmatamento (EUDR)</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Amazon deforestation falls 42% to a record low. Deforestation in the Brazilian Amazon has fallen to the lowest level on record. Data released today by Brazil&amp;#8217;s national space research institute, INPE, shows that forest clearing in Earth&amp;#8217;s largest rainforest over the 12 months ended July 31, 2026, amounted to 3,335 square kilometers (1,288 square miles), an area smaller than the Spanish</t>
+          <t>These tropical trees breathe at night to survive drought. Some tropical trees have evolved a clever way to survive drought by taking in carbon dioxide at night, allowing them to keep their pores closed during the hot daytime and conserve water. By comparing three Clusia species, researchers discovered that this water-saving form of photosynthesis, known as CAM, did not arise through a single evolu</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/short-article/2026/10/amazon-deforestation-falls-42-to-a-record-low/</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260922005712.htm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Embrapa Notícias</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Chefe-geral da Embrapa Gado de Corte integra lista das 100 Mulheres Poderosas do Agro</t>
+          <t>324-million-year-old fossil reveals how insects conquered land. Ancient fossils suggest insects conquered land through a long amphibious phase rather than making an abrupt jump from water to dry ground. A newly identified 324-million-year-old species still carried paddle-like abdominal limbs, revealing an evolutionary bridge between aquatic ancestors and modern six-legged insects.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.embrapa.br/busca-de-noticias/-/noticia/148959410/chefe-geral-da-embrapa-gado-de-corte-integra-lista-das-100-mulheres-poderosas-do-agro?p_auth=sKBJQ0xo#p_buscanoticia_WAR_pcebusca</t>
+          <t>https://www.sciencedaily.com/releases/2026/08/260827010455.htm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Embrapa Notícias</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Após décadas sendo comandada por homens, Mariana de Aragão Pereira se tornou, no início deste ano, a primeira mulher a assumir o cargo de chefe-geral da Embrapa Gado de Corte, em Campo Grande (MS)....</t>
+          <t xml:space="preserve">Alaska’s monster tsunami sent water 1,580 feet up a mountain. A massive landslide in Alaska triggered the second-highest tsunami ever recorded, sending water and debris 1,580 feet up a mountainside just hours after tourists visited the area. Scientists discovered that the disaster was preceded by several warning signs, including rapid glacier retreat, heavy rainfall, and thousands of tiny seismic </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.embrapa.br/busca-de-noticias</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261018205047.htm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CGIAR News</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>International Livestock Research Institute (ILRI)</t>
+          <t>Earth’s center is moving, and NASA just measured it. Earth’s center of mass is constantly on the move, shifting by a few millimeters as enormous amounts of water, ice, and even air migrate around the planet with the seasons. NASA scientists have developed a more precise way to track these tiny swings using laser-ranging satellites, GPS data, and measurements of how water and ice deform Earth’s cru</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.cgiar.org/news-events/</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261005071520.htm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CGIAR News</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>News October 16, 2026 How growing forage for livestock turned a small plot into a thriving family business In Ethiopia's Hadiya Zone, smallholder farmers are turning small plots of oats into profitable forage seed businesses that provide supplementary... internal</t>
+          <t>Scientists just found a new way to make hydrogen from water. A new light-activated material can efficiently produce hydrogen from water without requiring an additional expensive metal catalyst. Researchers say its unusual sulfur-based chemistry could point toward cheaper and more practical ways to turn sunlight into clean fuel.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.cgiar.org/news-events/</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261001214017.htm</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CGIAR News</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>How growing forage for livestock turned a small plot into a thriving family business</t>
+          <t>These tropical trees breathe at night to survive drought. Some tropical trees have evolved a clever way to survive drought by taking in carbon dioxide at night, allowing them to keep their pores closed during the hot daytime and conserve water. By comparing three Clusia species, researchers discovered that this water-saving form of photosynthesis, known as CAM, did not arise through a single evolu</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.cgiar.org/news-events/</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260922005712.htm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7088,24 +7088,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">A 24-year study uncovers a surprising climate benefit beneath forests. Scientists have discovered that some forest soils are becoming surprisingly better at removing methane from the atmosphere as temperatures rise and rainfall declines. A study spanning up to 24 years found methane absorption increasing by an average of 3% annually, challenging previous predictions about climate change's effects </t>
+          <t>One of America’s largest reservoirs just hit a record low. Lake Powell has fallen to its lowest level on record after an exceptionally dry and warm winter left the Colorado River Basin with little mountain snow to melt. Lake Mead also reached record lows, raising concerns for a river system that supplies water and power to more than 40 million people. Federal officials have taken emergency steps t</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261014015525.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260922005701.htm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7115,24 +7115,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>The U.S. Eradicated this flesh-eating parasite. Now it’s back. The flesh eating New World screwworm has returned to the United States, threatening livestock, wildlife, pets and potentially people as it spreads north. A new UC San Diego tracking system aims to predict where the parasite could strike next while officials revive the eradication strategy that defeated it decades ago.</t>
+          <t>Scientists “truly astonished” by discovery that challenges Earth’s origin story. A new study suggests Earth formed almost entirely from material in the inner Solar System, challenging the idea that water-rich material from beyond Jupiter played a major role. If correct, Earth’s water may have been present much closer to the young Sun than scientists previously thought.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260914102439.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260915232132.htm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7142,19 +7142,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Scientists finally solved how H5N1 bird flu hid in dairy cows. Researchers uncovered why H5N1 bird flu attacks cows’ udders instead of their lungs: the virus’s preferred receptors are concentrated in mammary tissue. The breakthrough could help scientists predict future bird flu jumps and spot unusual infections before they spread widely.</t>
+          <t xml:space="preserve">Irrigation’s climate benefit could equal 363 years of its own emissions. U.S. irrigation produces some greenhouse gas emissions, but new research suggests it prevents vastly more by allowing farmers to grow more food on less land. Without irrigation, replacing lost crop yields could require converting natural ecosystems into farmland, releasing an estimated 6.86 gigatons of greenhouse gases. That </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/06/260620100315.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260915232119.htm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7169,19 +7169,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">A 24-year study uncovers a surprising climate benefit beneath forests. Scientists have discovered that some forest soils are becoming surprisingly better at removing methane from the atmosphere as temperatures rise and rainfall declines. A study spanning up to 24 years found methane absorption increasing by an average of 3% annually, challenging previous predictions about climate change's effects </t>
+          <t>This German submarine sank in 1917. It’s still leaking TNT. A World War I submarine wreck off Denmark is leaking TNT into the surrounding water, seabed, and marine life more than a century after it sank. Scientists warn that thousands of similar wrecks could pose growing environmental risks as they continue to corrode.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261014015525.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260913081919.htm</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7196,19 +7196,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Scientists may have misread a 2-billion-year-old clue about Earth. Scientists have found that a famous 2-billion-year-old chemical signature, once thought to record a massive global change in Earth’s carbon cycle, may instead have been produced by local magma, hydrocarbons, and methane-eating microbes. The discovery raises new questions about what was really happening as oxygen transformed the you</t>
+          <t>One Mount Etna eruption took weeks. Another happened in hours. Mount Etna’s ancient eruptions followed radically different paths, with some magma lingering near the surface for weeks while other magma raced upward from nearly 30 kilometers deep in just hours. Scientists traced the difference to volcanic gases such as carbon dioxide and water, offering a powerful new way to understand and potential</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260925093201.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260912220100.htm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7223,39 +7223,39 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Scientists stunned as volcano cloud starts destroying methane. The Hunga Tonga eruption may have triggered a surprising chemical reaction that destroyed some of the methane released into the atmosphere. Scientists say the discovery could reshape estimates of methane pollution and inspire new methods for slowing near-term global warming.</t>
+          <t>Scientists find water was fueling volcanoes 3 billion years ago. Ancient rocks from Western Australia suggest water was reaching deep inside Earth more than three billion years ago, long before modern plate tectonics may have fully developed. Researchers propose that water-rich pieces of crust periodically sank into the mantle through a process they call “dripduction.” The buried water then helped</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260915095750.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260911214305.htm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pecuária sustentável, metano e bem-estar animal</t>
+          <t>Segurança hídrica, irrigação e saneamento</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Agência Fapesp</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Manejo adequado transforma pastagens degradadas em reservatórios de carbono. Experimentos de longa duração no interior paulista revelam que a intensificação moderada do pasto não apenas recupera a produtividade da terra, mas maximiza o sequestro de CO 2 . Pesquisa também validou método mais barato de medição</t>
+          <t xml:space="preserve">Extreme drought now covers 44% of Puerto Rico. Puerto Rico’s normally rainy season has instead brought a severe and fast-growing drought. By August 25, three-quarters of the territory was in at least moderate drought, with extreme drought covering 44 percent and some areas receiving less than 20 percent of their usual rainfall. Water shortages have forced rationing, while farmers are losing crops </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://agencia.fapesp.br/manejo-adequado-transforma-pastagens-degradadas-em-reservatorios-de-carbono/59417</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260902234457.htm</t>
         </is>
       </c>
     </row>
@@ -7267,22 +7267,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FAPESP - Oportunidades</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>A pesquisa será desenvolvida no âmbito do CEPID CEMol e tem como foco a engenharia de superfície de fotoanodos semicondutores à base de BiVO4 e Fe2TiO5 para aplicação na divisão fotoeletroquímica da água visando à produção de hidrogênio verde. O projeto envolve a deposição de filmes...</t>
+          <t>Earth may have lost the Sun’s protective shield millions of years ago. NASA-funded studies suggest Earth’s climate has been influenced by both the Sun’s travels through dense regions of the Milky Way and the violent superflares of its youth. Those events may help explain ancient ice ages as well as how early Earth stayed warm enough for liquid water when the Sun was much dimmer.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://fapesp.br/oportunidades</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260901070523.htm</t>
         </is>
       </c>
     </row>
@@ -7294,22 +7294,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FAO Newsroom</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>congresso</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>World Food Forum 2026: FAO calls for smarter water governance to safeguard food security</t>
+          <t>Scientists find a huge hidden ice reservoir beneath Utah’s mountains. Beneath the rocky slopes of Mount Timpanogos lies far more ice than anyone walking across the surface might suspect. Researchers used gravity measurements to map the buried glacier in 3D and found it is about 83% ice, with enough frozen water to fill 600 Olympic swimming pools. Their findings suggest rock glaciers form as fallin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.fao.org/newsroom/detail/world-food-forum-2026--fao-calls-for-smarter-water-governance-to-safeguard-food-security/en</t>
+          <t>https://www.sciencedaily.com/releases/2026/08/260827010459.htm</t>
         </is>
       </c>
     </row>
@@ -7321,22 +7321,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FAO Newsroom</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>congresso</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FAO launches digital platform to guide sustainable irrigation investment</t>
+          <t xml:space="preserve">Why are these lynxes washing their food?. Camera traps in Spain have captured a behavior never documented before in a wild cat: Iberian lynxes soaking their prey in water before eating it. Over five years, researchers recorded multiple females carrying dead rabbits to water troughs and repeatedly dunking them underwater. Scientists aren&amp;#8217;t sure why. The behavior may help lynxes stay hydrated </t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.fao.org/newsroom/en</t>
+          <t>https://news.mongabay.com/short-article/2026/10/why-are-these-lynxes-washing-their-food/</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CGIAR News</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CGIAR works with partners in six major regions to jointly address challenges to food, land, and water systems.</t>
+          <t>Conservation is bringing species back. Governments must help those gains last. &amp;#160; An old elephant can remember where to find water when the usual pools have dried. Her death leaves the herd with fewer ways to survive a drought. As elephants travel, they also carry seeds in their guts, depositing them far from the trees where they fed. In a forest emptied of large birds and [&amp;#8230;]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.cgiar.org/news-events/</t>
+          <t>https://news.mongabay.com/2026/10/conservation-is-bringing-species-back-governments-must-help-those-gains-last/</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CGIAR News</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7385,105 +7385,105 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>International Water Management Institute (IWMI)</t>
+          <t>‘Enclosed river:’ Women shellfish gatherers fight for access to mangroves in Brazil. Adriana Hora dos Santos stands waist-deep in the water. Her dark hair is tied in a single braid; her arms and torso covered by a pink Lycra shirt. The thick mangrove mud reaches her thighs. Using a machete just over 40-centimeters (16-inches) long, she pries dozens of oysters from the twisted roots with a steady [</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.cgiar.org/news-events/</t>
+          <t>https://news.mongabay.com/2026/10/enclosed-river-women-shellfish-gatherers-fight-for-access-to-mangroves-in-brazil/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Saúde única, zoonoses e doenças tropicais</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CGIAR News</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>News October 16, 2026 Strengthening Local Leadership to Protect Fisheries and Water Resources in Cambodia In Cambodia’s Tonle Sap floodplains, water connects farms, fisheries, ecosystems and communities. internal</t>
+          <t>Bird flu is spreading. Your backyard feeder could make it worse. Backyard bird feeders could become unexpected hotspots for H5N1 as Australia’s bird flu outbreak spreads, bringing species together in ways that rarely occur naturally. Experts say stopping feeding is safest, while smaller amounts of food, no hand-feeding, and careful cleaning can reduce the danger.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.cgiar.org/news-events/</t>
+          <t>https://www.sciencedaily.com/releases/2026/08/260824065519.htm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Sensoriamento remoto, satélites e geotecnologias</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CGIAR News</t>
+          <t>FAPESP - Oportunidades</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Strengthening Local Leadership to Protect Fisheries and Water Resources in Cambodia</t>
+          <t>Bolsa 1 – Digital Twin e restauração da rede O bolsista desenvolverá um modelo de Gêmeo Digital para simular a operação de estações de recarga de ônibus elétricos em situações de eventos climáticos extremos e propor estratégias de restauração da rede de distribuição por meio de...</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.cgiar.org/news-events/</t>
+          <t>https://fapesp.br/oportunidades/centro-de-inovacao-em-resiliencia-urbana-e-energetica-(cirue)/9875/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Sensoriamento remoto, satélites e geotecnologias</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CGIAR News</t>
+          <t>BNDES - Chamadas públicas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>In Cambodia’s Tonle Sap floodplains, water connects farms, fisheries, ecosystems and communities.</t>
+          <t>Radar da Transparência Pública</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.cgiar.org/news-events/</t>
+          <t>https://radardatransparencia.atricon.org.br/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Sensoriamento remoto, satélites e geotecnologias</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7493,24 +7493,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>New “plant armor” more than triples strawberry yields. A new protective fabric boosted strawberry yields by as much as 3.56 times while blocking insects and still allowing sunlight, rain, and airflow to reach the plants. Originally inspired by research on military clothing, Plant Armor could also help farms reduce pesticide and water use.</t>
+          <t>Something strange is happening beneath a volcano near 2 million people. Scientists have discovered evidence of two hidden magma sources beneath Nicaragua’s Masaya volcano, where satellite observations revealed mysterious ground movements suggesting magma is shifting deep underground. The findings could improve eruption forecasting for the active volcano, which sits near 2 million people and attrac</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260930020257.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261018205039.htm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Sensoriamento remoto, satélites e geotecnologias</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7520,24 +7520,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>These tropical trees breathe at night to survive drought. Some tropical trees have evolved a clever way to survive drought by taking in carbon dioxide at night, allowing them to keep their pores closed during the hot daytime and conserve water. By comparing three Clusia species, researchers discovered that this water-saving form of photosynthesis, known as CAM, did not arise through a single evolu</t>
+          <t>Arctic sea ice hits another troubling low in 2026. Arctic sea ice is shrinking in both winter and summer, with satellite records revealing that the region's remaining ice is becoming thinner, younger, and more vulnerable to melting. Despite a recent slowdown in summer losses, scientists warn that the Arctic could experience a nearly ice-free summer before 2050.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260922005712.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261015073212.htm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Sensoriamento remoto, satélites e geotecnologias</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7547,19 +7547,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>324-million-year-old fossil reveals how insects conquered land. Ancient fossils suggest insects conquered land through a long amphibious phase rather than making an abrupt jump from water to dry ground. A newly identified 324-million-year-old species still carried paddle-like abdominal limbs, revealing an evolutionary bridge between aquatic ancestors and modern six-legged insects.</t>
+          <t>Europe's new Sentinel-3C satellite just sent back spectacular images of Earth. Europe's Sentinel-3C satellite has returned breathtaking images of Earth just two weeks after launch, revealing the snowy Alps, frozen Arctic islands, and brilliant turquoise Caribbean waters. Its first measurements also show promising results for tracking rising seas, melting ice sheets, and other changes reshaping our</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/08/260827010455.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261011211559.htm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Sensoriamento remoto, satélites e geotecnologias</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7574,51 +7574,51 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alaska’s monster tsunami sent water 1,580 feet up a mountain. A massive landslide in Alaska triggered the second-highest tsunami ever recorded, sending water and debris 1,580 feet up a mountainside just hours after tourists visited the area. Scientists discovered that the disaster was preceded by several warning signs, including rapid glacier retreat, heavy rainfall, and thousands of tiny seismic </t>
+          <t>NASA captures a stunning transformation in Australia's red outback. Australia's normally dry, rust-colored outback has erupted into a spectacular carpet of wildflowers after unusually heavy rains, potentially producing its most impressive bloom in nearly 20 years. NASA satellite images capture the stunning transformation, which has even brought rare flowers to the grounds of a remote deep-space ob</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261018205047.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261008102710.htm</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Sensoriamento remoto, satélites e geotecnologias</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Earth’s center is moving, and NASA just measured it. Earth’s center of mass is constantly on the move, shifting by a few millimeters as enormous amounts of water, ice, and even air migrate around the planet with the seasons. NASA scientists have developed a more precise way to track these tiny swings using laser-ranging satellites, GPS data, and measurements of how water and ice deform Earth’s cru</t>
+          <t>Amazon deforestation falls 42% to a record low. Deforestation in the Brazilian Amazon has fallen to the lowest level on record. Data released today by Brazil&amp;#8217;s national space research institute, INPE, shows that forest clearing in Earth&amp;#8217;s largest rainforest over the 12 months ended July 31, 2026, amounted to 3,335 square kilometers (1,288 square miles), an area smaller than the Spanish</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261005071520.htm</t>
+          <t>https://news.mongabay.com/short-article/2026/10/amazon-deforestation-falls-42-to-a-record-low/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Robótica, drones e automação agrícola</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7628,51 +7628,51 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Scientists just found a new way to make hydrogen from water. A new light-activated material can efficiently produce hydrogen from water without requiring an additional expensive metal catalyst. Researchers say its unusual sulfur-based chemistry could point toward cheaper and more practical ways to turn sunlight into clean fuel.</t>
+          <t>Honey bees have their own personal flight paths and fly them with stunning precision. Researchers tracked honey bees in the wild using a drone-based system and found that each bee follows its own highly consistent flight path. Some repeated their routes so precisely that they flew only centimeters from where they had flown before. Landmarks like trees helped keep them on track, while uniform areas</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261001214017.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/06/260614011857.htm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Manejo integrado do fogo e queimadas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>These tropical trees breathe at night to survive drought. Some tropical trees have evolved a clever way to survive drought by taking in carbon dioxide at night, allowing them to keep their pores closed during the hot daytime and conserve water. By comparing three Clusia species, researchers discovered that this water-saving form of photosynthesis, known as CAM, did not arise through a single evolu</t>
+          <t xml:space="preserve">‘Perpetuating stupidity’: Indonesia comes under fire for response to burning and haze. JAKARTA — Indonesia is facing growing criticism over its response to a forest and land fire crisis that has sent choking haze billowing into neighboring Malaysia and Singapore, but officials insist the government is not to blame. The president has claimed that a drawdown in firefighting efforts means the number </t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260922005712.htm</t>
+          <t>https://news.mongabay.com/2026/10/perpetuating-stupidity-indonesia-comes-under-fire-for-response-to-burning-and-haze/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Alimentos, proteínas alternativas e agregação de valor</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7682,46 +7682,46 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>One of America’s largest reservoirs just hit a record low. Lake Powell has fallen to its lowest level on record after an exceptionally dry and warm winter left the Colorado River Basin with little mountain snow to melt. Lake Mead also reached record lows, raising concerns for a river system that supplies water and power to more than 40 million people. Federal officials have taken emergency steps t</t>
+          <t>Scientists just discovered how queen bees are really made. For decades, scientists thought royal jelly was the secret ingredient that turned an ordinary honeybee larva into a queen. New research reveals the process is far more remarkable: young worker bees create special “royal cribs” made from customized wax, carefully regulate warmth and humidity, and dedicate entire teams of attendants to raisi</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260922005701.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/06/260623083101.htm</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Economia circular, biomateriais e resíduos do agro</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>FAPESP - Oportunidades</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Scientists “truly astonished” by discovery that challenges Earth’s origin story. A new study suggests Earth formed almost entirely from material in the inner Solar System, challenging the idea that water-rich material from beyond Jupiter played a major role. If correct, Earth’s water may have been present much closer to the young Sun than scientists previously thought.</t>
+          <t>Direct Doctorate Fellowship in Chemical Recycling Instituition: Faculdade de Tecnologia / Universidade Estadual de Campinas City: Limeira Deadline for submissions: 2026-10-30 ...</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260915232132.htm</t>
+          <t>https://fapesp.br/oportunidades/environmental-conversion-of-municipal-waste-to-chemicals-and-biofuels-(ecometab):-integrating-experimental-quantum-mechanics-machine-learning-life-cycle-assessment-and-techno-economic-analysis/9929/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Economia circular, biomateriais e resíduos do agro</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7736,19 +7736,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Irrigation’s climate benefit could equal 363 years of its own emissions. U.S. irrigation produces some greenhouse gas emissions, but new research suggests it prevents vastly more by allowing farmers to grow more food on less land. Without irrigation, replacing lost crop yields could require converting natural ecosystems into farmland, releasing an estimated 6.86 gigatons of greenhouse gases. That </t>
+          <t>Scientists uncover the 2.3-billion-year-old secret that helped keep Earth habitable. Scientists may have solved a 2.3-billion-year-old mystery about how Earth maintained enough oxygen to support life. Ancient rocks reveal that phosphorus recycling in the oceans created a self-sustaining cycle that helped keep oxygen levels high, even as the planet underwent dramatic environmental changes. The disc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260915232119.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261011211602.htm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Economia circular, biomateriais e resíduos do agro</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7763,19 +7763,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>This German submarine sank in 1917. It’s still leaking TNT. A World War I submarine wreck off Denmark is leaking TNT into the surrounding water, seabed, and marine life more than a century after it sank. Scientists warn that thousands of similar wrecks could pose growing environmental risks as they continue to corrode.</t>
+          <t>This new concrete is stronger and pulls CO2 from the air. Researchers have created a concrete mixture that is both stronger and capable of absorbing carbon dioxide. The best formula, combining zeolite with bamboo biochar, boosted compressive strength by 7.48% and tensile strength by 15% compared with conventional concrete. It also captured about 1.2 grams of CO₂ per day in laboratory testing.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260913081919.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260921081105.htm</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Economia circular, biomateriais e resíduos do agro</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7790,105 +7790,105 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>One Mount Etna eruption took weeks. Another happened in hours. Mount Etna’s ancient eruptions followed radically different paths, with some magma lingering near the surface for weeks while other magma raced upward from nearly 30 kilometers deep in just hours. Scientists traced the difference to volcanic gases such as carbon dioxide and water, offering a powerful new way to understand and potential</t>
+          <t>Billions in rare earth elements may be hiding in America’s coal ash. Scientists are looking to diatoms, sea sponges, and plants for a cleaner way to recover rare earth elements and other valuable minerals hidden inside coal ash, red mud, and mine tailings. The bio-inspired approach could turn massive industrial waste piles into useful materials while reducing energy use, harsh chemicals, and relia</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260912220100.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260918024759.htm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Economia circular, biomateriais e resíduos do agro</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Scientists find water was fueling volcanoes 3 billion years ago. Ancient rocks from Western Australia suggest water was reaching deep inside Earth more than three billion years ago, long before modern plate tectonics may have fully developed. Researchers propose that water-rich pieces of crust periodically sank into the mantle through a process they call “dripduction.” The buried water then helped</t>
+          <t>Plastic industry bookkeeping plans hide chemical recycling harms, critics say. Plastic pollution has rapidly escalated into a global environmental crisis that threatens ecosystem function and human health at an epic scale. Solutions are urgently needed, but while scientists, conservationists and more than 75 nations have called for binding limits on fossil fuel-driven plastic production, the plast</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260911214305.htm</t>
+          <t>https://news.mongabay.com/2026/10/plastic-industry-bookkeeping-plans-hide-chemical-recycling-harms-critics-say/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Economia circular, biomateriais e resíduos do agro</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extreme drought now covers 44% of Puerto Rico. Puerto Rico’s normally rainy season has instead brought a severe and fast-growing drought. By August 25, three-quarters of the territory was in at least moderate drought, with extreme drought covering 44 percent and some areas receiving less than 20 percent of their usual rainfall. Water shortages have forced rationing, while farmers are losing crops </t>
+          <t>Climate change could send more toxic mining waste into coastal waters, study warns. Demand for metals has exploded in recent decades, thanks to population growth, technological innovation, and economic development. The volume of metal ores like iron and copper extracted globally quadrupled during the last half-century, and the trillion-dollar industry shows no signs of slowing down. But the growin</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260902234457.htm</t>
+          <t>https://news.mongabay.com/2026/10/climate-change-could-send-more-toxic-mining-waste-into-coastal-waters-study-warns/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>FAPESP - Oportunidades</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Earth may have lost the Sun’s protective shield millions of years ago. NASA-funded studies suggest Earth’s climate has been influenced by both the Sun’s travels through dense regions of the Milky Way and the violent superflares of its youth. Those events may help explain ancient ice ages as well as how early Earth stayed warm enough for liquid water when the Sun was much dimmer.</t>
+          <t>A pesquisa será desenvolvida no âmbito do CEPID CEMol e tem como foco a engenharia de superfície de fotoanodos semicondutores à base de BiVO4 e Fe2TiO5 para aplicação na divisão fotoeletroquímica da água visando à produção de hidrogênio verde. O projeto envolve a deposição de filmes...</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260901070523.htm</t>
+          <t>https://fapesp.br/oportunidades/engenharia-de-superficie-de-fotoanodos-de-bivo4-e-fe2tio5-para-divisao-fotoeletroquimica-da-Água/9914/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Nature Sustainability</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7898,267 +7898,267 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Scientists find a huge hidden ice reservoir beneath Utah’s mountains. Beneath the rocky slopes of Mount Timpanogos lies far more ice than anyone walking across the surface might suspect. Researchers used gravity measurements to map the buried glacier in 3D and found it is about 83% ice, with enough frozen water to fill 600 Olympic swimming pools. Their findings suggest rock glaciers form as fallin</t>
+          <t>Material circularity implications of battery degradation in shared electric mobility.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/08/260827010459.htm</t>
+          <t>https://www.nature.com/articles/s41893-026-01969-7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why are these lynxes washing their food?. Camera traps in Spain have captured a behavior never documented before in a wild cat: Iberian lynxes soaking their prey in water before eating it. Over five years, researchers recorded multiple females carrying dead rabbits to water troughs and repeatedly dunking them underwater. Scientists aren&amp;#8217;t sure why. The behavior may help lynxes stay hydrated </t>
+          <t>More trees can mean fewer birds, new study reveals. Trees planted to protect farmland from wind may not be the biodiversity boost many assume. In Japan’s wetland farming landscapes, shelterbelts benefited some birds but sharply reduced grassland and wetland species that need open space. Researchers found grassland bird abundance dropped by more than 70% near shelterbelts.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/short-article/2026/10/why-are-these-lynxes-washing-their-food/</t>
+          <t>https://www.sciencedaily.com/releases/2026/06/260620100426.htm</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Conservation is bringing species back. Governments must help those gains last. &amp;#160; An old elephant can remember where to find water when the usual pools have dried. Her death leaves the herd with fewer ways to survive a drought. As elephants travel, they also carry seeds in their guts, depositing them far from the trees where they fed. In a forest emptied of large birds and [&amp;#8230;]</t>
+          <t>Scientists just found a new way to make hydrogen from water. A new light-activated material can efficiently produce hydrogen from water without requiring an additional expensive metal catalyst. Researchers say its unusual sulfur-based chemistry could point toward cheaper and more practical ways to turn sunlight into clean fuel.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/2026/10/conservation-is-bringing-species-back-governments-must-help-those-gains-last/</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261001214017.htm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Segurança hídrica, irrigação e saneamento</t>
+          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>‘Enclosed river:’ Women shellfish gatherers fight for access to mangroves in Brazil. Adriana Hora dos Santos stands waist-deep in the water. Her dark hair is tied in a single braid; her arms and torso covered by a pink Lycra shirt. The thick mangrove mud reaches her thighs. Using a machete just over 40-centimeters (16-inches) long, she pries dozens of oysters from the twisted roots with a steady [</t>
+          <t>Scientists “truly astonished” by discovery that challenges Earth’s origin story. A new study suggests Earth formed almost entirely from material in the inner Solar System, challenging the idea that water-rich material from beyond Jupiter played a major role. If correct, Earth’s water may have been present much closer to the young Sun than scientists previously thought.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/2026/10/enclosed-river-women-shellfish-gatherers-fight-for-access-to-mangroves-in-brazil/</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260915232132.htm</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Saúde única, zoonoses e doenças tropicais</t>
+          <t>Segurança alimentar, nutrição e cadeias curtas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ScienceDaily Agricultura</t>
+          <t>FAO Newsroom</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>congresso</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Bird flu is spreading. Your backyard feeder could make it worse. Backyard bird feeders could become unexpected hotspots for H5N1 as Australia’s bird flu outbreak spreads, bringing species together in ways that rarely occur naturally. Experts say stopping feeding is safest, while smaller amounts of food, no hand-feeding, and careful cleaning can reduce the danger.</t>
+          <t>World Food Forum 2026 closes with renewed commitment to end hunger</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/08/260824065519.htm</t>
+          <t>https://www.fao.org/newsroom/detail/world-food-forum-2026-closes-with-renewed-commitment-to-end-hunger/en</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Segurança alimentar, nutrição e cadeias curtas</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FAPESP - Oportunidades</t>
+          <t>FAO Newsroom</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>congresso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Bolsa 1 – Digital Twin e restauração da rede O bolsista desenvolverá um modelo de Gêmeo Digital para simular a operação de estações de recarga de ônibus elétricos em situações de eventos climáticos extremos e propor estratégias de restauração da rede de distribuição por meio de...</t>
+          <t>World Food Forum 2026: FAO calls for smarter water governance to safeguard food security</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://fapesp.br/oportunidades</t>
+          <t>https://www.fao.org/newsroom/detail/world-food-forum-2026--fao-calls-for-smarter-water-governance-to-safeguard-food-security/en</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Segurança alimentar, nutrição e cadeias curtas</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>FAO Newsroom</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>congresso</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Sistemas de Inteligência Geoespacial</t>
+          <t>Africa’s potato potential: The path to food security and resilience</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.fao.org/newsroom/fao-blog/detail/fao-blog/2026/06/03/africa-s-potato-potential--the-path-to-food-security-and-resilience/en</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Segurança alimentar, nutrição e cadeias curtas</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>FAO Newsroom</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>congresso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sistemas de sensoriamento</t>
+          <t>Progress on hunger continues, but Africa and new crises raise concerns: FAO Chief Economist</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.fao.org/newsroom/detail/progress-on-hunger-continues--but-africa-and-new-crises-raise-concerns--fao-chief-economist/en</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Segurança alimentar, nutrição e cadeias curtas</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BNDES - Chamadas públicas</t>
+          <t>CGIAR News</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Radar da Transparência Pública</t>
+          <t>News October 16, 2026 How growing forage for livestock turned a small plot into a thriving family business In Ethiopia's Hadiya Zone, smallholder farmers are turning small plots of oats into profitable forage seed businesses that provide supplementary... internal</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.bndes.gov.br/wps/portal/site/home/transparencia/chamadas-publicas</t>
+          <t>https://www.cgiar.org/news-events/news/how-growing-forage-livestock-turned-small-plot-thriving-family-business</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Segurança alimentar, nutrição e cadeias curtas</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BNDES - Chamadas públicas</t>
+          <t>Nature Food</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>O BNDES obteve o selo Diamante na edição 2025 da avaliação anual conduzida pela Associação dos Membros dos Tribunais de Contas do Brasil (Atricon). Saiba mais sobre o Radar da Transparência Pública .</t>
+          <t>Zero hunger is not achievable without peace.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.bndes.gov.br/wps/portal/site/home/transparencia/chamadas-publicas</t>
+          <t>https://www.nature.com/articles/s43016-026-01439-5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Segurança alimentar, nutrição e cadeias curtas</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8168,1252 +8168,226 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Something strange is happening beneath a volcano near 2 million people. Scientists have discovered evidence of two hidden magma sources beneath Nicaragua’s Masaya volcano, where satellite observations revealed mysterious ground movements suggesting magma is shifting deep underground. The findings could improve eruption forecasting for the active volcano, which sits near 2 million people and attrac</t>
+          <t>Ant brains reveal how evolution turned hunger into parenting. Ant parenting may have evolved from the same brain systems that once controlled hunger. Researchers found that two chemical signals push clonal raider ants toward either caring for larvae or leaving to forage, with the balance changing as the ants grow older. Similar signals are involved in mammalian caregiving, suggesting that evolutio</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261018205039.htm</t>
+          <t>https://www.sciencedaily.com/releases/2026/07/260729051519.htm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Segurança alimentar, nutrição e cadeias curtas</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Arctic sea ice hits another troubling low in 2026. Arctic sea ice is shrinking in both winter and summer, with satellite records revealing that the region's remaining ice is becoming thinner, younger, and more vulnerable to melting. Despite a recent slowdown in summer losses, scientists warn that the Arctic could experience a nearly ice-free summer before 2050.</t>
+          <t>World Mushroom Day: From food to plastic replacement. A mushroom is analogous to a flower on a plant — it’s the reproductive organ of a fungus, which protects and distributes fungal spores. Mushrooms are critical part of our ecosystems. For humans and other animals, mushrooms are also food. And they may be part of the solution for food security and solving the plastic [&amp;#8230;]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261015073212.htm</t>
+          <t>https://news.mongabay.com/short-article/2026/10/world-mushroom-day-from-food-to-plastic-replacement/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Melhoramento genético, edição gênica e fenotipagem</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>FAPESP - Oportunidades</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Europe's new Sentinel-3C satellite just sent back spectacular images of Earth. Europe's Sentinel-3C satellite has returned breathtaking images of Earth just two weeks after launch, revealing the snowy Alps, frozen Arctic islands, and brilliant turquoise Caribbean waters. Its first measurements also show promising results for tracking rising seas, melting ice sheets, and other changes reshaping our</t>
+          <t>Level 5-Technical Training Fellowship in Regenerative Veterinary Medicine Instituition: Soluções em Biotecnologia 3D - Engenharia Tecidual Ltda/3DBSTISSUES City: Campinas Deadline for submissions: 2026-10-20 ...</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261011211559.htm</t>
+          <t>https://fapesp.br/oportunidades/kit-comercial-de-membrana-eletrofiada-associada-ao-lisado-plaquetario-como-estrategia-de-engenharia-tecidual-para-aplicacao-em-medicina-regenerativa-veterinaria/9907/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Melhoramento genético, edição gênica e fenotipagem</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ScienceDaily Clima</t>
+          <t>FAPESP - Oportunidades</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ciencia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NASA captures a stunning transformation in Australia's red outback. Australia's normally dry, rust-colored outback has erupted into a spectacular carpet of wildflowers after unusually heavy rains, potentially producing its most impressive bloom in nearly 20 years. NASA satellite images capture the stunning transformation, which has even brought rare flowers to the grounds of a remote deep-space ob</t>
+          <t>Doctorate Fellowship in Biotechnology Instituition: Universidade de Sorocaba (Uniso) City: Sorocaba Deadline for submissions: 2026-10-30 ...</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261008102710.htm</t>
+          <t>https://fapesp.br/oportunidades/desenvolvimento-de-estrategias-avancadas-em-quimica-verde-aplicadas-a-biodegradacao-e-valorizacao-de-polimeros-fosseis/9852/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sensoriamento remoto, satélites e geotecnologias</t>
+          <t>Melhoramento genético, edição gênica e fenotipagem</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mongabay</t>
+          <t>FAPESP - Oportunidades</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>fomento_br</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Amazon deforestation falls 42% to a record low. Deforestation in the Brazilian Amazon has fallen to the lowest level on record. Data released today by Brazil&amp;#8217;s national space research institute, INPE, shows that forest clearing in Earth&amp;#8217;s largest rainforest over the 12 months ended July 31, 2026, amounted to 3,335 square kilometers (1,288 square miles), an area smaller than the Spanish</t>
+          <t>Master’s Fellowship in Biotechnology Instituition: Universidade de Sorocaba (Uniso) City: Sorocaba Deadline for submissions: 2026-10-30 ...</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.mongabay.com/short-article/2026/10/amazon-deforestation-falls-42-to-a-record-low/</t>
+          <t>https://fapesp.br/oportunidades/desenvolvimento-de-estrategias-avancadas-em-quimica-verde-aplicadas-a-biodegradacao-e-valorizacao-de-polimeros-fosseis/9853/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Robótica, drones e automação agrícola</t>
+          <t>Melhoramento genético, edição gênica e fenotipagem</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>ScienceDaily Agricultura</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Sistemas de Visão Computacional, Inteligência Artificial e Conectividade</t>
+          <t>This deep-sea enzyme survives heat that destroys most proteins. A deep-sea microbe uses an exceptionally heat-resistant enzyme to turn atmospheric nitrogen into ammonia at temperatures that would destroy most proteins. Its unusual structure and a newly observed reaction state may reveal an ancient, shared mechanism behind nitrogen fixation and could eventually inspire cleaner biotechnology and fer</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260918024810.htm</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Robótica, drones e automação agrícola</t>
+          <t>Melhoramento genético, edição gênica e fenotipagem</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>ScienceDaily Clima</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>ciencia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Sistemas para automação da manufatura</t>
+          <t>This deep-sea enzyme survives heat that destroys most proteins. A deep-sea microbe uses an exceptionally heat-resistant enzyme to turn atmospheric nitrogen into ammonia at temperatures that would destroy most proteins. Its unusual structure and a newly observed reaction state may reveal an ancient, shared mechanism behind nitrogen fixation and could eventually inspire cleaner biotechnology and fer</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260918024810.htm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Robótica, drones e automação agrícola</t>
+          <t>Melhoramento genético, edição gênica e fenotipagem</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Sistemas robóticos e automação</t>
+          <t xml:space="preserve">Legal gaps allow rampant pet trade, poaching reptiles and amphibians towards extinction. Spain’s law enforcement agency, the Civil Guard, announced on Sept. 25, 2026, that it seized 209 reptiles from breeding facilities in Jérica and Sot de Ferrer (Castellón), including critically endangered iguanas endemic to Fiji. Nearly half of the reptiles were protected under CITES, the global wildlife trade </t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://embrapii.org.br/</t>
+          <t>https://news.mongabay.com/2026/10/legal-gaps-allow-rampant-pet-trade-poaching-reptiles-and-amphibians-towards-extinction/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Robótica, drones e automação agrícola</t>
+          <t>Melhoramento genético, edição gênica e fenotipagem</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Embrapii</t>
+          <t>Mongabay</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>fomento_br</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tecnologias Avançadas de Manufatura, Laser e Robótica</t>
+          <t xml:space="preserve">Cambodia was told to clean up its monkey trade. Regulators say it still hasn’t. CHIANG MAI, Thailand — Global wildlife trade authorities say Cambodia has made little progress in cleaning up its monkey export industry, a year after the country was flagged as needing major reforms in how it manages the capture, breeding, and export of monkeys used in biomedical research. In November 2025, following </t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
-        <is>
-          <t>https://embrapii.org.br/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Robótica, drones e automação agrícola</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>ScienceDaily Agricultura</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Honey bees have their own personal flight paths and fly them with stunning precision. Researchers tracked honey bees in the wild using a drone-based system and found that each bee follows its own highly consistent flight path. Some repeated their routes so precisely that they flew only centimeters from where they had flown before. Landmarks like trees helped keep them on track, while uniform areas</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/06/260614011857.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Manejo integrado do fogo e queimadas</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Mongabay</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>noticia</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‘Perpetuating stupidity’: Indonesia comes under fire for response to burning and haze. JAKARTA — Indonesia is facing growing criticism over its response to a forest and land fire crisis that has sent choking haze billowing into neighboring Malaysia and Singapore, but officials insist the government is not to blame. The president has claimed that a drawdown in firefighting efforts means the number </t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>https://news.mongabay.com/2026/10/perpetuating-stupidity-indonesia-comes-under-fire-for-response-to-burning-and-haze/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Alimentos, proteínas alternativas e agregação de valor</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>FAPESP - Oportunidades</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Level 4-Technical Training Fellowship in Food Safety Instituition: Faculdade de Engenharia de Alimentos, Universidade Estadual de Campinas (FEA-Unicamp) City: Campinas Deadline for submissions: 2026-10-30 ...</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>https://fapesp.br/oportunidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Alimentos, proteínas alternativas e agregação de valor</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Embrapii</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Processamento de Biomassa para Biocombustíveis</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>https://embrapii.org.br/</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Alimentos, proteínas alternativas e agregação de valor</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Embrapa Notícias</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>noticia</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>O aplicativo Monitora Caju foi tema do Café com Negócios, realizada pela Embrapa Agroindústria Tropical, no dia 14 de outubro. Em sua quinta edição, o evento contou com a participação do...</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>https://www.embrapa.br/busca-de-noticias</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Alimentos, proteínas alternativas e agregação de valor</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>ScienceDaily Agricultura</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Scientists just discovered how queen bees are really made. For decades, scientists thought royal jelly was the secret ingredient that turned an ordinary honeybee larva into a queen. New research reveals the process is far more remarkable: young worker bees create special “royal cribs” made from customized wax, carefully regulate warmth and humidity, and dedicate entire teams of attendants to raisi</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/06/260623083101.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Economia circular, biomateriais e resíduos do agro</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>FAPESP - Oportunidades</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Direct Doctorate Fellowship in Chemical Recycling Instituition: Faculdade de Tecnologia / Universidade Estadual de Campinas City: Limeira Deadline for submissions: 2026-10-30 ...</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>https://fapesp.br/oportunidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Economia circular, biomateriais e resíduos do agro</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Embrapii</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Processamento de Biomassa para Biocombustíveis</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>https://embrapii.org.br/</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Economia circular, biomateriais e resíduos do agro</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Embrapii</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Transformação de Biomassa</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>https://embrapii.org.br/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Economia circular, biomateriais e resíduos do agro</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>ScienceDaily Clima</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Scientists uncover the 2.3-billion-year-old secret that helped keep Earth habitable. Scientists may have solved a 2.3-billion-year-old mystery about how Earth maintained enough oxygen to support life. Ancient rocks reveal that phosphorus recycling in the oceans created a self-sustaining cycle that helped keep oxygen levels high, even as the planet underwent dramatic environmental changes. The disc</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261011211602.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Economia circular, biomateriais e resíduos do agro</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>ScienceDaily Clima</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>This new concrete is stronger and pulls CO2 from the air. Researchers have created a concrete mixture that is both stronger and capable of absorbing carbon dioxide. The best formula, combining zeolite with bamboo biochar, boosted compressive strength by 7.48% and tensile strength by 15% compared with conventional concrete. It also captured about 1.2 grams of CO₂ per day in laboratory testing.</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260921081105.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Economia circular, biomateriais e resíduos do agro</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>ScienceDaily Clima</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Billions in rare earth elements may be hiding in America’s coal ash. Scientists are looking to diatoms, sea sponges, and plants for a cleaner way to recover rare earth elements and other valuable minerals hidden inside coal ash, red mud, and mine tailings. The bio-inspired approach could turn massive industrial waste piles into useful materials while reducing energy use, harsh chemicals, and relia</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260918024759.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Economia circular, biomateriais e resíduos do agro</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Mongabay</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>noticia</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Plastic industry bookkeeping plans hide chemical recycling harms, critics say. Plastic pollution has rapidly escalated into a global environmental crisis that threatens ecosystem function and human health at an epic scale. Solutions are urgently needed, but while scientists, conservationists and more than 75 nations have called for binding limits on fossil fuel-driven plastic production, the plast</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>https://news.mongabay.com/2026/10/plastic-industry-bookkeeping-plans-hide-chemical-recycling-harms-critics-say/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Economia circular, biomateriais e resíduos do agro</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Mongabay</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>noticia</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Climate change could send more toxic mining waste into coastal waters, study warns. Demand for metals has exploded in recent decades, thanks to population growth, technological innovation, and economic development. The volume of metal ores like iron and copper extracted globally quadrupled during the last half-century, and the trillion-dollar industry shows no signs of slowing down. But the growin</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>https://news.mongabay.com/2026/10/climate-change-could-send-more-toxic-mining-waste-into-coastal-waters-study-warns/</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>FAPESP - Oportunidades</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>A pesquisa será desenvolvida no âmbito do CEPID CEMol e tem como foco a engenharia de superfície de fotoanodos semicondutores à base de BiVO4 e Fe2TiO5 para aplicação na divisão fotoeletroquímica da água visando à produção de hidrogênio verde. O projeto envolve a deposição de filmes...</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>https://fapesp.br/oportunidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Embrapii</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Tecnologias Inovadoras para Descarbonização Industrial e Transição Energética</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>https://embrapii.org.br/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Nature Sustainability</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Material circularity implications of battery degradation in shared electric mobility.</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>https://www.nature.com/articles/s41893-026-01969-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>ScienceDaily Agricultura</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>More trees can mean fewer birds, new study reveals. Trees planted to protect farmland from wind may not be the biodiversity boost many assume. In Japan’s wetland farming landscapes, shelterbelts benefited some birds but sharply reduced grassland and wetland species that need open space. Researchers found grassland bird abundance dropped by more than 70% near shelterbelts.</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/06/260620100426.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>ScienceDaily Clima</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Scientists just found a new way to make hydrogen from water. A new light-activated material can efficiently produce hydrogen from water without requiring an additional expensive metal catalyst. Researchers say its unusual sulfur-based chemistry could point toward cheaper and more practical ways to turn sunlight into clean fuel.</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/10/261001214017.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Transição energética: solar, hidrogênio verde e eletrificação</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>ScienceDaily Clima</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Scientists “truly astonished” by discovery that challenges Earth’s origin story. A new study suggests Earth formed almost entirely from material in the inner Solar System, challenging the idea that water-rich material from beyond Jupiter played a major role. If correct, Earth’s water may have been present much closer to the young Sun than scientists previously thought.</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260915232132.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>FAO Newsroom</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>congresso</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>World Food Forum 2026 closes with renewed commitment to end hunger</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/newsroom/detail/world-food-forum-2026-closes-with-renewed-commitment-to-end-hunger/en</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>FAO Newsroom</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>congresso</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>World Food Forum 2026: FAO calls for smarter water governance to safeguard food security</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/newsroom/detail/world-food-forum-2026--fao-calls-for-smarter-water-governance-to-safeguard-food-security/en</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>FAO Newsroom</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>congresso</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Africa’s potato potential: The path to food security and resilience</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/newsroom/fao-blog/detail/fao-blog/2026/06/03/africa-s-potato-potential--the-path-to-food-security-and-resilience/en</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>FAO Newsroom</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>congresso</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>In sub-Saharan Africa, where hunger and malnutrition remain acute challenges, potatoes offer a powerful opportunity. Around 33 million smallholder farmers — roughly 80 percent— depend on crops like potatoes for both food and income.</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/newsroom/en</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>FAO Newsroom</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>congresso</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Progress on hunger continues, but Africa and new crises raise concerns: FAO Chief Economist</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/newsroom/detail/progress-on-hunger-continues--but-africa-and-new-crises-raise-concerns--fao-chief-economist/en</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>CGIAR News</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>noticia</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>News October 16, 2026 How growing forage for livestock turned a small plot into a thriving family business In Ethiopia's Hadiya Zone, smallholder farmers are turning small plots of oats into profitable forage seed businesses that provide supplementary... internal</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>https://www.cgiar.org/news-events/</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>CGIAR News</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>noticia</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>In Ethiopia's Hadiya Zone, smallholder farmers are turning small plots of oats into profitable forage seed businesses that provide supplementary...</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>https://www.cgiar.org/news-events/</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Nature Food</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Zero hunger is not achievable without peace.</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>https://www.nature.com/articles/s43016-026-01439-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>ScienceDaily Agricultura</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Ant brains reveal how evolution turned hunger into parenting. Ant parenting may have evolved from the same brain systems that once controlled hunger. Researchers found that two chemical signals push clonal raider ants toward either caring for larvae or leaving to forage, with the balance changing as the ants grow older. Similar signals are involved in mammalian caregiving, suggesting that evolutio</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/07/260729051519.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Segurança alimentar, nutrição e cadeias curtas</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Mongabay</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>noticia</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>World Mushroom Day: From food to plastic replacement. A mushroom is analogous to a flower on a plant — it’s the reproductive organ of a fungus, which protects and distributes fungal spores. Mushrooms are critical part of our ecosystems. For humans and other animals, mushrooms are also food. And they may be part of the solution for food security and solving the plastic [&amp;#8230;]</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>https://news.mongabay.com/short-article/2026/10/world-mushroom-day-from-food-to-plastic-replacement/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Melhoramento genético, edição gênica e fenotipagem</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>FAPESP - Oportunidades</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Level 5-Technical Training Fellowship in Regenerative Veterinary Medicine Instituition: Soluções em Biotecnologia 3D - Engenharia Tecidual Ltda/3DBSTISSUES City: Campinas Deadline for submissions: 2026-10-20 ...</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>https://fapesp.br/oportunidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Melhoramento genético, edição gênica e fenotipagem</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>FAPESP - Oportunidades</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Doctorate Fellowship in Biotechnology Instituition: Universidade de Sorocaba (Uniso) City: Sorocaba Deadline for submissions: 2026-10-30 ...</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>https://fapesp.br/oportunidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Melhoramento genético, edição gênica e fenotipagem</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>FAPESP - Oportunidades</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Master’s Fellowship in Biotechnology Instituition: Universidade de Sorocaba (Uniso) City: Sorocaba Deadline for submissions: 2026-10-30 ...</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>https://fapesp.br/oportunidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Melhoramento genético, edição gênica e fenotipagem</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Embrapii</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>fomento_br</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Biotecnologia aplicada à micropropagação vegetal</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>https://embrapii.org.br/</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Melhoramento genético, edição gênica e fenotipagem</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>ScienceDaily Agricultura</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>This deep-sea enzyme survives heat that destroys most proteins. A deep-sea microbe uses an exceptionally heat-resistant enzyme to turn atmospheric nitrogen into ammonia at temperatures that would destroy most proteins. Its unusual structure and a newly observed reaction state may reveal an ancient, shared mechanism behind nitrogen fixation and could eventually inspire cleaner biotechnology and fer</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260918024810.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Melhoramento genético, edição gênica e fenotipagem</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>ScienceDaily Clima</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>ciencia</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>This deep-sea enzyme survives heat that destroys most proteins. A deep-sea microbe uses an exceptionally heat-resistant enzyme to turn atmospheric nitrogen into ammonia at temperatures that would destroy most proteins. Its unusual structure and a newly observed reaction state may reveal an ancient, shared mechanism behind nitrogen fixation and could eventually inspire cleaner biotechnology and fer</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260918024810.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Melhoramento genético, edição gênica e fenotipagem</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Mongabay</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>noticia</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Legal gaps allow rampant pet trade, poaching reptiles and amphibians towards extinction. Spain’s law enforcement agency, the Civil Guard, announced on Sept. 25, 2026, that it seized 209 reptiles from breeding facilities in Jérica and Sot de Ferrer (Castellón), including critically endangered iguanas endemic to Fiji. Nearly half of the reptiles were protected under CITES, the global wildlife trade </t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>https://news.mongabay.com/2026/10/legal-gaps-allow-rampant-pet-trade-poaching-reptiles-and-amphibians-towards-extinction/</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Melhoramento genético, edição gênica e fenotipagem</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Mongabay</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>noticia</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cambodia was told to clean up its monkey trade. Regulators say it still hasn’t. CHIANG MAI, Thailand — Global wildlife trade authorities say Cambodia has made little progress in cleaning up its monkey export industry, a year after the country was flagged as needing major reforms in how it manages the capture, breeding, and export of monkeys used in biomedical research. In November 2025, following </t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
         <is>
           <t>https://news.mongabay.com/2026/10/cambodia-was-told-to-clean-up-its-monkey-trade-regulators-say-it-still-hasnt/</t>
         </is>
